--- a/m2.xlsx
+++ b/m2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\سعيات\م2 - ف2\steam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1877AE08-B0E2-4985-9FFC-8802B9B4A93C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C2B636-328C-458A-B629-72D0A5E910C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -436,7 +436,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -459,6 +459,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -474,7 +489,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -497,20 +512,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -521,16 +527,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -813,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E830AE-5C32-4A25-A5BE-EAB4941C3B09}">
-  <dimension ref="A1:P123"/>
+  <dimension ref="A1:P320"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
@@ -834,45 +842,45 @@
     <col min="16" max="16" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="6"/>
+      <c r="E1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5" t="s">
+      <c r="F1" s="6"/>
+      <c r="G1" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="H1" s="5"/>
-      <c r="I1" s="4" t="s">
+      <c r="H1" s="6"/>
+      <c r="I1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4" t="s">
+      <c r="J1" s="6"/>
+      <c r="K1" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4" t="s">
+      <c r="L1" s="6"/>
+      <c r="M1" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4" t="s">
+      <c r="N1" s="6"/>
+      <c r="O1" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="P1" s="4"/>
+      <c r="P1" s="6"/>
     </row>
     <row r="2" spans="1:16" ht="21" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
@@ -947,6 +955,16 @@
       <c r="J3" s="2">
         <v>8</v>
       </c>
+      <c r="K3" s="2">
+        <v>22</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
     </row>
     <row r="4" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
@@ -979,6 +997,16 @@
       <c r="J4" s="2">
         <v>7</v>
       </c>
+      <c r="K4" s="2">
+        <v>15</v>
+      </c>
+      <c r="L4" s="2">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
     </row>
     <row r="5" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
@@ -1011,6 +1039,16 @@
       <c r="J5" s="2">
         <v>8</v>
       </c>
+      <c r="K5" s="2">
+        <v>27</v>
+      </c>
+      <c r="L5" s="2">
+        <v>4</v>
+      </c>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
     </row>
     <row r="6" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
@@ -1043,6 +1081,16 @@
       <c r="J6" s="2">
         <v>8</v>
       </c>
+      <c r="K6" s="2">
+        <v>35</v>
+      </c>
+      <c r="L6" s="2">
+        <v>8</v>
+      </c>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
     </row>
     <row r="7" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
@@ -1075,6 +1123,16 @@
       <c r="J7" s="2">
         <v>8</v>
       </c>
+      <c r="K7" s="2">
+        <v>15</v>
+      </c>
+      <c r="L7" s="2">
+        <v>5</v>
+      </c>
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
     </row>
     <row r="8" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A8" s="3">
@@ -1107,6 +1165,16 @@
       <c r="J8" s="2">
         <v>8</v>
       </c>
+      <c r="K8" s="2">
+        <v>37</v>
+      </c>
+      <c r="L8" s="2">
+        <v>8</v>
+      </c>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
     </row>
     <row r="9" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A9" s="3">
@@ -1139,6 +1207,16 @@
       <c r="J9" s="2">
         <v>8</v>
       </c>
+      <c r="K9" s="2">
+        <v>35</v>
+      </c>
+      <c r="L9" s="2">
+        <v>6</v>
+      </c>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
     </row>
     <row r="10" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A10" s="3">
@@ -1171,6 +1249,16 @@
       <c r="J10" s="2">
         <v>8</v>
       </c>
+      <c r="K10" s="2">
+        <v>28</v>
+      </c>
+      <c r="L10" s="2">
+        <v>8</v>
+      </c>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
     </row>
     <row r="11" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A11" s="3">
@@ -1203,6 +1291,16 @@
       <c r="J11" s="2">
         <v>9</v>
       </c>
+      <c r="K11" s="2">
+        <v>26</v>
+      </c>
+      <c r="L11" s="2">
+        <v>8</v>
+      </c>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
     </row>
     <row r="12" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A12" s="3">
@@ -1235,6 +1333,16 @@
       <c r="J12" s="2">
         <v>9</v>
       </c>
+      <c r="K12" s="2">
+        <v>17</v>
+      </c>
+      <c r="L12" s="2">
+        <v>2</v>
+      </c>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
     </row>
     <row r="13" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A13" s="3">
@@ -1267,6 +1375,16 @@
       <c r="J13" s="2">
         <v>9</v>
       </c>
+      <c r="K13" s="2">
+        <v>28</v>
+      </c>
+      <c r="L13" s="2">
+        <v>10</v>
+      </c>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
     </row>
     <row r="14" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A14" s="3">
@@ -1299,6 +1417,16 @@
       <c r="J14" s="2">
         <v>9</v>
       </c>
+      <c r="K14" s="2">
+        <v>15</v>
+      </c>
+      <c r="L14" s="2">
+        <v>5</v>
+      </c>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
     </row>
     <row r="15" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A15" s="3">
@@ -1331,6 +1459,16 @@
       <c r="J15" s="2">
         <v>8</v>
       </c>
+      <c r="K15" s="2">
+        <v>23</v>
+      </c>
+      <c r="L15" s="2">
+        <v>6</v>
+      </c>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
     </row>
     <row r="16" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A16" s="3">
@@ -1363,8 +1501,18 @@
       <c r="J16" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K16" s="2">
+        <v>20</v>
+      </c>
+      <c r="L16" s="2">
+        <v>6</v>
+      </c>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+    </row>
+    <row r="17" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A17" s="3">
         <v>2015</v>
       </c>
@@ -1395,8 +1543,18 @@
       <c r="J17" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K17" s="2">
+        <v>23</v>
+      </c>
+      <c r="L17" s="2">
+        <v>6</v>
+      </c>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+    </row>
+    <row r="18" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A18" s="3">
         <v>2016</v>
       </c>
@@ -1427,8 +1585,16 @@
       <c r="J18" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K18" s="2">
+        <v>0</v>
+      </c>
+      <c r="L18" s="2"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+    </row>
+    <row r="19" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A19" s="3">
         <v>2017</v>
       </c>
@@ -1459,8 +1625,18 @@
       <c r="J19" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K19" s="2">
+        <v>33</v>
+      </c>
+      <c r="L19" s="2">
+        <v>6</v>
+      </c>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+    </row>
+    <row r="20" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A20" s="3">
         <v>2018</v>
       </c>
@@ -1491,8 +1667,18 @@
       <c r="J20" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K20" s="2">
+        <v>28</v>
+      </c>
+      <c r="L20" s="2">
+        <v>8</v>
+      </c>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+    </row>
+    <row r="21" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="3">
         <v>2019</v>
       </c>
@@ -1523,8 +1709,18 @@
       <c r="J21" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K21" s="2">
+        <v>20</v>
+      </c>
+      <c r="L21" s="2">
+        <v>4</v>
+      </c>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+    </row>
+    <row r="22" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A22" s="3">
         <v>2020</v>
       </c>
@@ -1555,8 +1751,18 @@
       <c r="J22" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K22" s="2">
+        <v>18</v>
+      </c>
+      <c r="L22" s="2">
+        <v>4</v>
+      </c>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+    </row>
+    <row r="23" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A23" s="3">
         <v>2021</v>
       </c>
@@ -1587,8 +1793,18 @@
       <c r="J23" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K23" s="2">
+        <v>16</v>
+      </c>
+      <c r="L23" s="2">
+        <v>2</v>
+      </c>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+    </row>
+    <row r="24" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A24" s="3">
         <v>2022</v>
       </c>
@@ -1619,8 +1835,18 @@
       <c r="J24" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K24" s="2">
+        <v>26</v>
+      </c>
+      <c r="L24" s="2">
+        <v>6</v>
+      </c>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+    </row>
+    <row r="25" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A25" s="3">
         <v>2023</v>
       </c>
@@ -1651,8 +1877,18 @@
       <c r="J25" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K25" s="2">
+        <v>26</v>
+      </c>
+      <c r="L25" s="2">
+        <v>6</v>
+      </c>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+    </row>
+    <row r="26" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A26" s="3">
         <v>2024</v>
       </c>
@@ -1683,8 +1919,18 @@
       <c r="J26" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K26" s="2">
+        <v>19</v>
+      </c>
+      <c r="L26" s="2">
+        <v>2</v>
+      </c>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+    </row>
+    <row r="27" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A27" s="3">
         <v>2025</v>
       </c>
@@ -1715,8 +1961,18 @@
       <c r="J27" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K27" s="2">
+        <v>16</v>
+      </c>
+      <c r="L27" s="2">
+        <v>2</v>
+      </c>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+    </row>
+    <row r="28" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A28" s="3">
         <v>2026</v>
       </c>
@@ -1747,8 +2003,18 @@
       <c r="J28" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K28" s="2">
+        <v>26</v>
+      </c>
+      <c r="L28" s="2">
+        <v>8</v>
+      </c>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+    </row>
+    <row r="29" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A29" s="3">
         <v>2027</v>
       </c>
@@ -1779,8 +2045,16 @@
       <c r="J29" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K29" s="2">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+    </row>
+    <row r="30" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A30" s="3">
         <v>2028</v>
       </c>
@@ -1811,8 +2085,18 @@
       <c r="J30" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K30" s="2">
+        <v>37</v>
+      </c>
+      <c r="L30" s="2">
+        <v>10</v>
+      </c>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+    </row>
+    <row r="31" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A31" s="3">
         <v>2029</v>
       </c>
@@ -1843,8 +2127,18 @@
       <c r="J31" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K31" s="2">
+        <v>29</v>
+      </c>
+      <c r="L31" s="2">
+        <v>4</v>
+      </c>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+    </row>
+    <row r="32" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A32" s="3">
         <v>2030</v>
       </c>
@@ -1875,8 +2169,18 @@
       <c r="J32" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K32" s="2">
+        <v>17</v>
+      </c>
+      <c r="L32" s="2">
+        <v>2</v>
+      </c>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+    </row>
+    <row r="33" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A33" s="3">
         <v>2031</v>
       </c>
@@ -1907,8 +2211,18 @@
       <c r="J33" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K33" s="2">
+        <v>22</v>
+      </c>
+      <c r="L33" s="2">
+        <v>2</v>
+      </c>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+    </row>
+    <row r="34" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A34" s="3">
         <v>2032</v>
       </c>
@@ -1939,8 +2253,18 @@
       <c r="J34" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K34" s="2">
+        <v>20</v>
+      </c>
+      <c r="L34" s="2">
+        <v>1</v>
+      </c>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+    </row>
+    <row r="35" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A35" s="3">
         <v>2033</v>
       </c>
@@ -1971,8 +2295,18 @@
       <c r="J35" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K35" s="2">
+        <v>21</v>
+      </c>
+      <c r="L35" s="2">
+        <v>2</v>
+      </c>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+    </row>
+    <row r="36" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A36" s="3">
         <v>2034</v>
       </c>
@@ -2003,8 +2337,18 @@
       <c r="J36" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K36" s="2">
+        <v>40</v>
+      </c>
+      <c r="L36" s="2">
+        <v>10</v>
+      </c>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+    </row>
+    <row r="37" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A37" s="3">
         <v>2035</v>
       </c>
@@ -2035,8 +2379,18 @@
       <c r="J37" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K37" s="2">
+        <v>13</v>
+      </c>
+      <c r="L37" s="2">
+        <v>2</v>
+      </c>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+    </row>
+    <row r="38" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A38" s="3">
         <v>2036</v>
       </c>
@@ -2067,8 +2421,18 @@
       <c r="J38" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K38" s="2">
+        <v>24</v>
+      </c>
+      <c r="L38" s="2">
+        <v>4</v>
+      </c>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+    </row>
+    <row r="39" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A39" s="3">
         <v>2037</v>
       </c>
@@ -2099,8 +2463,18 @@
       <c r="J39" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K39" s="2">
+        <v>16</v>
+      </c>
+      <c r="L39" s="2">
+        <v>2</v>
+      </c>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+    </row>
+    <row r="40" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A40" s="3">
         <v>2038</v>
       </c>
@@ -2131,8 +2505,18 @@
       <c r="J40" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K40" s="2">
+        <v>27</v>
+      </c>
+      <c r="L40" s="2">
+        <v>6</v>
+      </c>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+    </row>
+    <row r="41" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A41" s="3">
         <v>2039</v>
       </c>
@@ -2163,8 +2547,18 @@
       <c r="J41" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K41" s="2">
+        <v>25</v>
+      </c>
+      <c r="L41" s="2">
+        <v>1</v>
+      </c>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+    </row>
+    <row r="42" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A42" s="3">
         <v>2040</v>
       </c>
@@ -2195,8 +2589,18 @@
       <c r="J42" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K42" s="2">
+        <v>19</v>
+      </c>
+      <c r="L42" s="2">
+        <v>8</v>
+      </c>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5"/>
+    </row>
+    <row r="43" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A43" s="3">
         <v>2041</v>
       </c>
@@ -2227,8 +2631,18 @@
       <c r="J43" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K43" s="2">
+        <v>35</v>
+      </c>
+      <c r="L43" s="2">
+        <v>6</v>
+      </c>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+    </row>
+    <row r="44" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A44" s="3">
         <v>2042</v>
       </c>
@@ -2259,8 +2673,18 @@
       <c r="J44" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K44" s="2">
+        <v>37</v>
+      </c>
+      <c r="L44" s="2">
+        <v>8</v>
+      </c>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+    </row>
+    <row r="45" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A45" s="3">
         <v>2043</v>
       </c>
@@ -2291,8 +2715,18 @@
       <c r="J45" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K45" s="2">
+        <v>21</v>
+      </c>
+      <c r="L45" s="2">
+        <v>6</v>
+      </c>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+    </row>
+    <row r="46" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A46" s="3">
         <v>2044</v>
       </c>
@@ -2323,8 +2757,18 @@
       <c r="J46" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K46" s="2">
+        <v>35</v>
+      </c>
+      <c r="L46" s="2">
+        <v>8</v>
+      </c>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+    </row>
+    <row r="47" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A47" s="3">
         <v>2045</v>
       </c>
@@ -2355,8 +2799,18 @@
       <c r="J47" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K47" s="2">
+        <v>31</v>
+      </c>
+      <c r="L47" s="2">
+        <v>6</v>
+      </c>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+    </row>
+    <row r="48" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A48" s="3">
         <v>2046</v>
       </c>
@@ -2387,8 +2841,18 @@
       <c r="J48" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K48" s="2">
+        <v>40</v>
+      </c>
+      <c r="L48" s="2">
+        <v>10</v>
+      </c>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
+    </row>
+    <row r="49" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A49" s="3">
         <v>2047</v>
       </c>
@@ -2419,8 +2883,18 @@
       <c r="J49" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K49" s="2">
+        <v>23</v>
+      </c>
+      <c r="L49" s="2">
+        <v>4</v>
+      </c>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+    </row>
+    <row r="50" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A50" s="3">
         <v>2048</v>
       </c>
@@ -2451,8 +2925,18 @@
       <c r="J50" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K50" s="2">
+        <v>21</v>
+      </c>
+      <c r="L50" s="2">
+        <v>4</v>
+      </c>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+    </row>
+    <row r="51" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A51" s="3">
         <v>2049</v>
       </c>
@@ -2483,8 +2967,18 @@
       <c r="J51" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K51" s="2">
+        <v>28</v>
+      </c>
+      <c r="L51" s="2">
+        <v>4</v>
+      </c>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="5"/>
+    </row>
+    <row r="52" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A52" s="3">
         <v>2050</v>
       </c>
@@ -2515,8 +3009,18 @@
       <c r="J52" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K52" s="2">
+        <v>31</v>
+      </c>
+      <c r="L52" s="2">
+        <v>10</v>
+      </c>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+    </row>
+    <row r="53" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A53" s="3">
         <v>2051</v>
       </c>
@@ -2547,8 +3051,18 @@
       <c r="J53" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K53" s="2">
+        <v>30</v>
+      </c>
+      <c r="L53" s="2">
+        <v>8</v>
+      </c>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="5"/>
+    </row>
+    <row r="54" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A54" s="3">
         <v>2052</v>
       </c>
@@ -2579,8 +3093,18 @@
       <c r="J54" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K54" s="2">
+        <v>18</v>
+      </c>
+      <c r="L54" s="2">
+        <v>1</v>
+      </c>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="5"/>
+    </row>
+    <row r="55" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A55" s="3">
         <v>2053</v>
       </c>
@@ -2611,8 +3135,18 @@
       <c r="J55" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K55" s="2">
+        <v>28</v>
+      </c>
+      <c r="L55" s="2">
+        <v>8</v>
+      </c>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="5"/>
+    </row>
+    <row r="56" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A56" s="3">
         <v>2054</v>
       </c>
@@ -2643,8 +3177,18 @@
       <c r="J56" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K56" s="2">
+        <v>12</v>
+      </c>
+      <c r="L56" s="2">
+        <v>3</v>
+      </c>
+      <c r="M56" s="5"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="5"/>
+    </row>
+    <row r="57" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A57" s="3">
         <v>2055</v>
       </c>
@@ -2675,8 +3219,18 @@
       <c r="J57" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K57" s="2">
+        <v>26</v>
+      </c>
+      <c r="L57" s="2">
+        <v>8</v>
+      </c>
+      <c r="M57" s="5"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="5"/>
+    </row>
+    <row r="58" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A58" s="3">
         <v>2056</v>
       </c>
@@ -2707,8 +3261,18 @@
       <c r="J58" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K58" s="2">
+        <v>28</v>
+      </c>
+      <c r="L58" s="2">
+        <v>8</v>
+      </c>
+      <c r="M58" s="5"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="5"/>
+    </row>
+    <row r="59" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A59" s="3">
         <v>2057</v>
       </c>
@@ -2739,8 +3303,18 @@
       <c r="J59" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K59" s="2">
+        <v>23</v>
+      </c>
+      <c r="L59" s="2">
+        <v>4</v>
+      </c>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="5"/>
+    </row>
+    <row r="60" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A60" s="3">
         <v>2058</v>
       </c>
@@ -2771,8 +3345,18 @@
       <c r="J60" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K60" s="2">
+        <v>19</v>
+      </c>
+      <c r="L60" s="2">
+        <v>2</v>
+      </c>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="5"/>
+    </row>
+    <row r="61" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A61" s="3">
         <v>2059</v>
       </c>
@@ -2803,8 +3387,18 @@
       <c r="J61" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K61" s="2">
+        <v>15</v>
+      </c>
+      <c r="L61" s="2">
+        <v>1</v>
+      </c>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="5"/>
+    </row>
+    <row r="62" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A62" s="3">
         <v>2060</v>
       </c>
@@ -2835,8 +3429,18 @@
       <c r="J62" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K62" s="2">
+        <v>16</v>
+      </c>
+      <c r="L62" s="2">
+        <v>2</v>
+      </c>
+      <c r="M62" s="5"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="5"/>
+    </row>
+    <row r="63" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A63" s="3">
         <v>2061</v>
       </c>
@@ -2867,8 +3471,18 @@
       <c r="J63" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K63" s="2">
+        <v>23</v>
+      </c>
+      <c r="L63" s="2">
+        <v>2</v>
+      </c>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="5"/>
+    </row>
+    <row r="64" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A64" s="3">
         <v>2062</v>
       </c>
@@ -2899,8 +3513,18 @@
       <c r="J64" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K64" s="2">
+        <v>21</v>
+      </c>
+      <c r="L64" s="2">
+        <v>2</v>
+      </c>
+      <c r="M64" s="5"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="5"/>
+    </row>
+    <row r="65" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A65" s="3">
         <v>2063</v>
       </c>
@@ -2931,8 +3555,18 @@
       <c r="J65" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K65" s="2">
+        <v>14</v>
+      </c>
+      <c r="L65" s="2">
+        <v>8</v>
+      </c>
+      <c r="M65" s="5"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="5"/>
+    </row>
+    <row r="66" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A66" s="3">
         <v>2064</v>
       </c>
@@ -2963,8 +3597,18 @@
       <c r="J66" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K66" s="2">
+        <v>34</v>
+      </c>
+      <c r="L66" s="2">
+        <v>8</v>
+      </c>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="5"/>
+    </row>
+    <row r="67" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A67" s="3">
         <v>2065</v>
       </c>
@@ -2995,8 +3639,18 @@
       <c r="J67" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K67" s="2">
+        <v>18</v>
+      </c>
+      <c r="L67" s="2">
+        <v>6</v>
+      </c>
+      <c r="M67" s="5"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="5"/>
+    </row>
+    <row r="68" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A68" s="3">
         <v>2066</v>
       </c>
@@ -3027,8 +3681,18 @@
       <c r="J68" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K68" s="2">
+        <v>18</v>
+      </c>
+      <c r="L68" s="2">
+        <v>1</v>
+      </c>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="5"/>
+    </row>
+    <row r="69" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A69" s="3">
         <v>2067</v>
       </c>
@@ -3059,8 +3723,18 @@
       <c r="J69" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K69" s="2">
+        <v>29</v>
+      </c>
+      <c r="L69" s="2">
+        <v>8</v>
+      </c>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="5"/>
+    </row>
+    <row r="70" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A70" s="3">
         <v>2068</v>
       </c>
@@ -3091,8 +3765,18 @@
       <c r="J70" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K70" s="2">
+        <v>23</v>
+      </c>
+      <c r="L70" s="2">
+        <v>6</v>
+      </c>
+      <c r="M70" s="5"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="5"/>
+    </row>
+    <row r="71" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A71" s="3">
         <v>2069</v>
       </c>
@@ -3123,8 +3807,18 @@
       <c r="J71" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K71" s="2">
+        <v>26</v>
+      </c>
+      <c r="L71" s="2">
+        <v>6</v>
+      </c>
+      <c r="M71" s="5"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="5"/>
+    </row>
+    <row r="72" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A72" s="3">
         <v>2070</v>
       </c>
@@ -3155,8 +3849,18 @@
       <c r="J72" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K72" s="2">
+        <v>37</v>
+      </c>
+      <c r="L72" s="2">
+        <v>8</v>
+      </c>
+      <c r="M72" s="5"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="5"/>
+    </row>
+    <row r="73" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A73" s="3">
         <v>2071</v>
       </c>
@@ -3187,8 +3891,18 @@
       <c r="J73" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K73" s="2">
+        <v>23</v>
+      </c>
+      <c r="L73" s="2">
+        <v>6</v>
+      </c>
+      <c r="M73" s="5"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="5"/>
+    </row>
+    <row r="74" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A74" s="3">
         <v>2072</v>
       </c>
@@ -3219,8 +3933,18 @@
       <c r="J74" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K74" s="2">
+        <v>35</v>
+      </c>
+      <c r="L74" s="2">
+        <v>6</v>
+      </c>
+      <c r="M74" s="5"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="5"/>
+    </row>
+    <row r="75" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A75" s="3">
         <v>2073</v>
       </c>
@@ -3251,8 +3975,18 @@
       <c r="J75" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K75" s="2">
+        <v>10</v>
+      </c>
+      <c r="L75" s="2">
+        <v>4</v>
+      </c>
+      <c r="M75" s="5"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="5"/>
+    </row>
+    <row r="76" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A76" s="3">
         <v>2074</v>
       </c>
@@ -3283,8 +4017,18 @@
       <c r="J76" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K76" s="2">
+        <v>16</v>
+      </c>
+      <c r="L76" s="2">
+        <v>1</v>
+      </c>
+      <c r="M76" s="5"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="5"/>
+      <c r="P76" s="5"/>
+    </row>
+    <row r="77" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A77" s="3">
         <v>2075</v>
       </c>
@@ -3315,8 +4059,18 @@
       <c r="J77" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K77" s="2">
+        <v>32</v>
+      </c>
+      <c r="L77" s="2">
+        <v>8</v>
+      </c>
+      <c r="M77" s="5"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5"/>
+      <c r="P77" s="5"/>
+    </row>
+    <row r="78" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A78" s="3">
         <v>2076</v>
       </c>
@@ -3347,8 +4101,18 @@
       <c r="J78" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K78" s="2">
+        <v>29</v>
+      </c>
+      <c r="L78" s="2">
+        <v>8</v>
+      </c>
+      <c r="M78" s="5"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="5"/>
+      <c r="P78" s="5"/>
+    </row>
+    <row r="79" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A79" s="3">
         <v>2077</v>
       </c>
@@ -3379,8 +4143,18 @@
       <c r="J79" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K79" s="2">
+        <v>19</v>
+      </c>
+      <c r="L79" s="2">
+        <v>2</v>
+      </c>
+      <c r="M79" s="5"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5"/>
+      <c r="P79" s="5"/>
+    </row>
+    <row r="80" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A80" s="3">
         <v>2078</v>
       </c>
@@ -3411,8 +4185,18 @@
       <c r="J80" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K80" s="2">
+        <v>16</v>
+      </c>
+      <c r="L80" s="2">
+        <v>2</v>
+      </c>
+      <c r="M80" s="5"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="5"/>
+      <c r="P80" s="5"/>
+    </row>
+    <row r="81" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A81" s="3">
         <v>2079</v>
       </c>
@@ -3443,8 +4227,18 @@
       <c r="J81" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K81" s="2">
+        <v>21</v>
+      </c>
+      <c r="L81" s="2">
+        <v>4</v>
+      </c>
+      <c r="M81" s="5"/>
+      <c r="N81" s="5"/>
+      <c r="O81" s="5"/>
+      <c r="P81" s="5"/>
+    </row>
+    <row r="82" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A82" s="3">
         <v>2080</v>
       </c>
@@ -3475,8 +4269,18 @@
       <c r="J82" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K82" s="2">
+        <v>21</v>
+      </c>
+      <c r="L82" s="2">
+        <v>4</v>
+      </c>
+      <c r="M82" s="5"/>
+      <c r="N82" s="5"/>
+      <c r="O82" s="5"/>
+      <c r="P82" s="5"/>
+    </row>
+    <row r="83" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A83" s="3">
         <v>2081</v>
       </c>
@@ -3507,8 +4311,18 @@
       <c r="J83" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K83" s="2">
+        <v>22</v>
+      </c>
+      <c r="L83" s="2">
+        <v>4</v>
+      </c>
+      <c r="M83" s="5"/>
+      <c r="N83" s="5"/>
+      <c r="O83" s="5"/>
+      <c r="P83" s="5"/>
+    </row>
+    <row r="84" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A84" s="3">
         <v>2082</v>
       </c>
@@ -3539,8 +4353,18 @@
       <c r="J84" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K84" s="2">
+        <v>39</v>
+      </c>
+      <c r="L84" s="2">
+        <v>10</v>
+      </c>
+      <c r="M84" s="5"/>
+      <c r="N84" s="5"/>
+      <c r="O84" s="5"/>
+      <c r="P84" s="5"/>
+    </row>
+    <row r="85" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A85" s="3">
         <v>2083</v>
       </c>
@@ -3571,8 +4395,18 @@
       <c r="J85" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K85" s="2">
+        <v>22</v>
+      </c>
+      <c r="L85" s="2">
+        <v>4</v>
+      </c>
+      <c r="M85" s="5"/>
+      <c r="N85" s="5"/>
+      <c r="O85" s="5"/>
+      <c r="P85" s="5"/>
+    </row>
+    <row r="86" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A86" s="3">
         <v>2084</v>
       </c>
@@ -3603,8 +4437,18 @@
       <c r="J86" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="87" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K86" s="2">
+        <v>25</v>
+      </c>
+      <c r="L86" s="2">
+        <v>1</v>
+      </c>
+      <c r="M86" s="5"/>
+      <c r="N86" s="5"/>
+      <c r="O86" s="5"/>
+      <c r="P86" s="5"/>
+    </row>
+    <row r="87" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A87" s="3">
         <v>2085</v>
       </c>
@@ -3635,8 +4479,18 @@
       <c r="J87" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K87" s="2">
+        <v>32</v>
+      </c>
+      <c r="L87" s="2">
+        <v>8</v>
+      </c>
+      <c r="M87" s="5"/>
+      <c r="N87" s="5"/>
+      <c r="O87" s="5"/>
+      <c r="P87" s="5"/>
+    </row>
+    <row r="88" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A88" s="3">
         <v>2086</v>
       </c>
@@ -3667,8 +4521,18 @@
       <c r="J88" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="89" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K88" s="2">
+        <v>18</v>
+      </c>
+      <c r="L88" s="2">
+        <v>2</v>
+      </c>
+      <c r="M88" s="5"/>
+      <c r="N88" s="5"/>
+      <c r="O88" s="5"/>
+      <c r="P88" s="5"/>
+    </row>
+    <row r="89" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A89" s="3">
         <v>2087</v>
       </c>
@@ -3699,8 +4563,18 @@
       <c r="J89" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K89" s="2">
+        <v>28</v>
+      </c>
+      <c r="L89" s="2">
+        <v>2</v>
+      </c>
+      <c r="M89" s="5"/>
+      <c r="N89" s="5"/>
+      <c r="O89" s="5"/>
+      <c r="P89" s="5"/>
+    </row>
+    <row r="90" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A90" s="3">
         <v>2088</v>
       </c>
@@ -3731,8 +4605,18 @@
       <c r="J90" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="91" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K90" s="2">
+        <v>21</v>
+      </c>
+      <c r="L90" s="2">
+        <v>1</v>
+      </c>
+      <c r="M90" s="5"/>
+      <c r="N90" s="5"/>
+      <c r="O90" s="5"/>
+      <c r="P90" s="5"/>
+    </row>
+    <row r="91" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A91" s="3">
         <v>2089</v>
       </c>
@@ -3763,8 +4647,18 @@
       <c r="J91" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="92" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K91" s="2">
+        <v>25</v>
+      </c>
+      <c r="L91" s="2">
+        <v>8</v>
+      </c>
+      <c r="M91" s="5"/>
+      <c r="N91" s="5"/>
+      <c r="O91" s="5"/>
+      <c r="P91" s="5"/>
+    </row>
+    <row r="92" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A92" s="3">
         <v>2090</v>
       </c>
@@ -3795,8 +4689,18 @@
       <c r="J92" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="93" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K92" s="2">
+        <v>19</v>
+      </c>
+      <c r="L92" s="2">
+        <v>1</v>
+      </c>
+      <c r="M92" s="5"/>
+      <c r="N92" s="5"/>
+      <c r="O92" s="5"/>
+      <c r="P92" s="5"/>
+    </row>
+    <row r="93" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A93" s="3">
         <v>2091</v>
       </c>
@@ -3827,8 +4731,18 @@
       <c r="J93" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="94" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K93" s="2">
+        <v>35</v>
+      </c>
+      <c r="L93" s="2">
+        <v>6</v>
+      </c>
+      <c r="M93" s="5"/>
+      <c r="N93" s="5"/>
+      <c r="O93" s="5"/>
+      <c r="P93" s="5"/>
+    </row>
+    <row r="94" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A94" s="3">
         <v>2092</v>
       </c>
@@ -3859,8 +4773,18 @@
       <c r="J94" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="95" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K94" s="2">
+        <v>25</v>
+      </c>
+      <c r="L94" s="2">
+        <v>8</v>
+      </c>
+      <c r="M94" s="5"/>
+      <c r="N94" s="5"/>
+      <c r="O94" s="5"/>
+      <c r="P94" s="5"/>
+    </row>
+    <row r="95" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A95" s="3">
         <v>2093</v>
       </c>
@@ -3891,8 +4815,18 @@
       <c r="J95" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="96" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K95" s="2">
+        <v>26</v>
+      </c>
+      <c r="L95" s="2">
+        <v>2</v>
+      </c>
+      <c r="M95" s="5"/>
+      <c r="N95" s="5"/>
+      <c r="O95" s="5"/>
+      <c r="P95" s="5"/>
+    </row>
+    <row r="96" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A96" s="3">
         <v>2094</v>
       </c>
@@ -3923,8 +4857,18 @@
       <c r="J96" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="97" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K96" s="2">
+        <v>36</v>
+      </c>
+      <c r="L96" s="2">
+        <v>6</v>
+      </c>
+      <c r="M96" s="5"/>
+      <c r="N96" s="5"/>
+      <c r="O96" s="5"/>
+      <c r="P96" s="5"/>
+    </row>
+    <row r="97" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A97" s="3">
         <v>2095</v>
       </c>
@@ -3955,8 +4899,18 @@
       <c r="J97" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K97" s="2">
+        <v>17</v>
+      </c>
+      <c r="L97" s="2">
+        <v>2</v>
+      </c>
+      <c r="M97" s="5"/>
+      <c r="N97" s="5"/>
+      <c r="O97" s="5"/>
+      <c r="P97" s="5"/>
+    </row>
+    <row r="98" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A98" s="3">
         <v>2096</v>
       </c>
@@ -3987,8 +4941,18 @@
       <c r="J98" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="99" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K98" s="2">
+        <v>32</v>
+      </c>
+      <c r="L98" s="2">
+        <v>6</v>
+      </c>
+      <c r="M98" s="5"/>
+      <c r="N98" s="5"/>
+      <c r="O98" s="5"/>
+      <c r="P98" s="5"/>
+    </row>
+    <row r="99" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A99" s="3">
         <v>2097</v>
       </c>
@@ -4019,8 +4983,18 @@
       <c r="J99" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K99" s="2">
+        <v>27</v>
+      </c>
+      <c r="L99" s="2">
+        <v>4</v>
+      </c>
+      <c r="M99" s="5"/>
+      <c r="N99" s="5"/>
+      <c r="O99" s="5"/>
+      <c r="P99" s="5"/>
+    </row>
+    <row r="100" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A100" s="3">
         <v>2098</v>
       </c>
@@ -4051,8 +5025,18 @@
       <c r="J100" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="101" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K100" s="2">
+        <v>28</v>
+      </c>
+      <c r="L100" s="2">
+        <v>4</v>
+      </c>
+      <c r="M100" s="5"/>
+      <c r="N100" s="5"/>
+      <c r="O100" s="5"/>
+      <c r="P100" s="5"/>
+    </row>
+    <row r="101" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A101" s="3">
         <v>2099</v>
       </c>
@@ -4083,8 +5067,18 @@
       <c r="J101" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K101" s="2">
+        <v>24</v>
+      </c>
+      <c r="L101" s="2">
+        <v>4</v>
+      </c>
+      <c r="M101" s="5"/>
+      <c r="N101" s="5"/>
+      <c r="O101" s="5"/>
+      <c r="P101" s="5"/>
+    </row>
+    <row r="102" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A102" s="3">
         <v>2100</v>
       </c>
@@ -4115,8 +5109,18 @@
       <c r="J102" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="103" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K102" s="2">
+        <v>20</v>
+      </c>
+      <c r="L102" s="2">
+        <v>2</v>
+      </c>
+      <c r="M102" s="5"/>
+      <c r="N102" s="5"/>
+      <c r="O102" s="5"/>
+      <c r="P102" s="5"/>
+    </row>
+    <row r="103" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A103" s="3">
         <v>2101</v>
       </c>
@@ -4147,8 +5151,18 @@
       <c r="J103" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K103" s="2">
+        <v>24</v>
+      </c>
+      <c r="L103" s="2">
+        <v>6</v>
+      </c>
+      <c r="M103" s="5"/>
+      <c r="N103" s="5"/>
+      <c r="O103" s="5"/>
+      <c r="P103" s="5"/>
+    </row>
+    <row r="104" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A104" s="3">
         <v>2102</v>
       </c>
@@ -4179,8 +5193,18 @@
       <c r="J104" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="105" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K104" s="2">
+        <v>21</v>
+      </c>
+      <c r="L104" s="2">
+        <v>1</v>
+      </c>
+      <c r="M104" s="5"/>
+      <c r="N104" s="5"/>
+      <c r="O104" s="5"/>
+      <c r="P104" s="5"/>
+    </row>
+    <row r="105" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A105" s="3">
         <v>2103</v>
       </c>
@@ -4211,8 +5235,18 @@
       <c r="J105" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="106" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K105" s="2">
+        <v>23</v>
+      </c>
+      <c r="L105" s="2">
+        <v>6</v>
+      </c>
+      <c r="M105" s="5"/>
+      <c r="N105" s="5"/>
+      <c r="O105" s="5"/>
+      <c r="P105" s="5"/>
+    </row>
+    <row r="106" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A106" s="3">
         <v>2104</v>
       </c>
@@ -4243,8 +5277,18 @@
       <c r="J106" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="107" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K106" s="2">
+        <v>24</v>
+      </c>
+      <c r="L106" s="2">
+        <v>6</v>
+      </c>
+      <c r="M106" s="5"/>
+      <c r="N106" s="5"/>
+      <c r="O106" s="5"/>
+      <c r="P106" s="5"/>
+    </row>
+    <row r="107" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A107" s="3">
         <v>2105</v>
       </c>
@@ -4275,8 +5319,18 @@
       <c r="J107" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="108" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K107" s="2">
+        <v>16</v>
+      </c>
+      <c r="L107" s="2">
+        <v>1</v>
+      </c>
+      <c r="M107" s="5"/>
+      <c r="N107" s="5"/>
+      <c r="O107" s="5"/>
+      <c r="P107" s="5"/>
+    </row>
+    <row r="108" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A108" s="3">
         <v>2106</v>
       </c>
@@ -4307,8 +5361,18 @@
       <c r="J108" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="109" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K108" s="2">
+        <v>15</v>
+      </c>
+      <c r="L108" s="2">
+        <v>4</v>
+      </c>
+      <c r="M108" s="5"/>
+      <c r="N108" s="5"/>
+      <c r="O108" s="5"/>
+      <c r="P108" s="5"/>
+    </row>
+    <row r="109" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A109" s="3">
         <v>2107</v>
       </c>
@@ -4339,8 +5403,18 @@
       <c r="J109" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="110" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K109" s="2">
+        <v>23</v>
+      </c>
+      <c r="L109" s="2">
+        <v>8</v>
+      </c>
+      <c r="M109" s="5"/>
+      <c r="N109" s="5"/>
+      <c r="O109" s="5"/>
+      <c r="P109" s="5"/>
+    </row>
+    <row r="110" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A110" s="3">
         <v>2108</v>
       </c>
@@ -4371,8 +5445,18 @@
       <c r="J110" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="111" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K110" s="2">
+        <v>27</v>
+      </c>
+      <c r="L110" s="2">
+        <v>10</v>
+      </c>
+      <c r="M110" s="5"/>
+      <c r="N110" s="5"/>
+      <c r="O110" s="5"/>
+      <c r="P110" s="5"/>
+    </row>
+    <row r="111" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A111" s="3">
         <v>2109</v>
       </c>
@@ -4403,8 +5487,18 @@
       <c r="J111" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="112" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K111" s="2">
+        <v>18</v>
+      </c>
+      <c r="L111" s="2">
+        <v>6</v>
+      </c>
+      <c r="M111" s="5"/>
+      <c r="N111" s="5"/>
+      <c r="O111" s="5"/>
+      <c r="P111" s="5"/>
+    </row>
+    <row r="112" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A112" s="3">
         <v>2110</v>
       </c>
@@ -4435,8 +5529,16 @@
       <c r="J112" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K112" s="2">
+        <v>0</v>
+      </c>
+      <c r="L112" s="2"/>
+      <c r="M112" s="5"/>
+      <c r="N112" s="5"/>
+      <c r="O112" s="5"/>
+      <c r="P112" s="5"/>
+    </row>
+    <row r="113" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A113" s="3">
         <v>2111</v>
       </c>
@@ -4467,8 +5569,18 @@
       <c r="J113" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="114" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K113" s="2">
+        <v>14</v>
+      </c>
+      <c r="L113" s="2">
+        <v>2</v>
+      </c>
+      <c r="M113" s="5"/>
+      <c r="N113" s="5"/>
+      <c r="O113" s="5"/>
+      <c r="P113" s="5"/>
+    </row>
+    <row r="114" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A114" s="3">
         <v>2112</v>
       </c>
@@ -4499,8 +5611,18 @@
       <c r="J114" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K114" s="2">
+        <v>18</v>
+      </c>
+      <c r="L114" s="2">
+        <v>1</v>
+      </c>
+      <c r="M114" s="5"/>
+      <c r="N114" s="5"/>
+      <c r="O114" s="5"/>
+      <c r="P114" s="5"/>
+    </row>
+    <row r="115" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A115" s="3">
         <v>2113</v>
       </c>
@@ -4531,8 +5653,18 @@
       <c r="J115" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="116" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K115" s="2">
+        <v>16</v>
+      </c>
+      <c r="L115" s="2">
+        <v>1</v>
+      </c>
+      <c r="M115" s="5"/>
+      <c r="N115" s="5"/>
+      <c r="O115" s="5"/>
+      <c r="P115" s="5"/>
+    </row>
+    <row r="116" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A116" s="3">
         <v>2114</v>
       </c>
@@ -4563,8 +5695,18 @@
       <c r="J116" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="117" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K116" s="2">
+        <v>24</v>
+      </c>
+      <c r="L116" s="2">
+        <v>6</v>
+      </c>
+      <c r="M116" s="5"/>
+      <c r="N116" s="5"/>
+      <c r="O116" s="5"/>
+      <c r="P116" s="5"/>
+    </row>
+    <row r="117" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A117" s="3">
         <v>2115</v>
       </c>
@@ -4595,8 +5737,18 @@
       <c r="J117" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="118" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K117" s="2">
+        <v>19</v>
+      </c>
+      <c r="L117" s="2">
+        <v>1</v>
+      </c>
+      <c r="M117" s="5"/>
+      <c r="N117" s="5"/>
+      <c r="O117" s="5"/>
+      <c r="P117" s="5"/>
+    </row>
+    <row r="118" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A118" s="3">
         <v>2116</v>
       </c>
@@ -4627,8 +5779,18 @@
       <c r="J118" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="119" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K118" s="2">
+        <v>20</v>
+      </c>
+      <c r="L118" s="2">
+        <v>6</v>
+      </c>
+      <c r="M118" s="5"/>
+      <c r="N118" s="5"/>
+      <c r="O118" s="5"/>
+      <c r="P118" s="5"/>
+    </row>
+    <row r="119" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A119" s="3">
         <v>2117</v>
       </c>
@@ -4659,8 +5821,18 @@
       <c r="J119" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="120" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K119" s="2">
+        <v>21</v>
+      </c>
+      <c r="L119" s="2">
+        <v>4</v>
+      </c>
+      <c r="M119" s="5"/>
+      <c r="N119" s="5"/>
+      <c r="O119" s="5"/>
+      <c r="P119" s="5"/>
+    </row>
+    <row r="120" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A120" s="3">
         <v>2118</v>
       </c>
@@ -4691,8 +5863,18 @@
       <c r="J120" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="121" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K120" s="2">
+        <v>36</v>
+      </c>
+      <c r="L120" s="2">
+        <v>10</v>
+      </c>
+      <c r="M120" s="5"/>
+      <c r="N120" s="5"/>
+      <c r="O120" s="5"/>
+      <c r="P120" s="5"/>
+    </row>
+    <row r="121" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A121" s="3">
         <v>2119</v>
       </c>
@@ -4723,8 +5905,18 @@
       <c r="J121" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="122" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K121" s="2">
+        <v>24</v>
+      </c>
+      <c r="L121" s="2">
+        <v>6</v>
+      </c>
+      <c r="M121" s="5"/>
+      <c r="N121" s="5"/>
+      <c r="O121" s="5"/>
+      <c r="P121" s="5"/>
+    </row>
+    <row r="122" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A122" s="3">
         <v>2120</v>
       </c>
@@ -4755,8 +5947,18 @@
       <c r="J122" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="123" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="K122" s="2">
+        <v>22</v>
+      </c>
+      <c r="L122" s="2">
+        <v>8</v>
+      </c>
+      <c r="M122" s="5"/>
+      <c r="N122" s="5"/>
+      <c r="O122" s="5"/>
+      <c r="P122" s="5"/>
+    </row>
+    <row r="123" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A123" s="3">
         <v>2121</v>
       </c>
@@ -4787,19 +5989,786 @@
       <c r="J123" s="2">
         <v>9</v>
       </c>
+      <c r="K123" s="2">
+        <v>30</v>
+      </c>
+      <c r="L123" s="2">
+        <v>10</v>
+      </c>
+      <c r="M123" s="5"/>
+      <c r="N123" s="5"/>
+      <c r="O123" s="5"/>
+      <c r="P123" s="5"/>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A195" s="7"/>
+      <c r="B195" s="7"/>
+      <c r="C195" s="7"/>
+      <c r="D195" s="7"/>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A196" s="7"/>
+      <c r="B196" s="7"/>
+      <c r="C196" s="7"/>
+      <c r="D196" s="7"/>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A197" s="7"/>
+      <c r="B197" s="7"/>
+      <c r="C197" s="7"/>
+      <c r="D197" s="7"/>
+    </row>
+    <row r="198" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A198" s="8"/>
+      <c r="B198" s="8"/>
+      <c r="C198" s="7"/>
+      <c r="D198" s="7"/>
+    </row>
+    <row r="199" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A199" s="9"/>
+      <c r="B199" s="9"/>
+      <c r="C199" s="7"/>
+      <c r="D199" s="7"/>
+    </row>
+    <row r="200" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A200" s="9"/>
+      <c r="B200" s="9"/>
+      <c r="C200" s="7"/>
+      <c r="D200" s="7"/>
+    </row>
+    <row r="201" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A201" s="9"/>
+      <c r="B201" s="9"/>
+      <c r="C201" s="7"/>
+      <c r="D201" s="7"/>
+    </row>
+    <row r="202" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A202" s="9"/>
+      <c r="B202" s="9"/>
+      <c r="C202" s="7"/>
+      <c r="D202" s="7"/>
+    </row>
+    <row r="203" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A203" s="9"/>
+      <c r="B203" s="9"/>
+      <c r="C203" s="7"/>
+      <c r="D203" s="7"/>
+    </row>
+    <row r="204" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A204" s="9"/>
+      <c r="B204" s="9"/>
+      <c r="C204" s="7"/>
+      <c r="D204" s="7"/>
+    </row>
+    <row r="205" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A205" s="9"/>
+      <c r="B205" s="9"/>
+      <c r="C205" s="7"/>
+      <c r="D205" s="7"/>
+    </row>
+    <row r="206" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A206" s="9"/>
+      <c r="B206" s="9"/>
+      <c r="C206" s="7"/>
+      <c r="D206" s="7"/>
+    </row>
+    <row r="207" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A207" s="9"/>
+      <c r="B207" s="9"/>
+      <c r="C207" s="7"/>
+      <c r="D207" s="7"/>
+    </row>
+    <row r="208" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A208" s="9"/>
+      <c r="B208" s="9"/>
+      <c r="C208" s="7"/>
+      <c r="D208" s="7"/>
+    </row>
+    <row r="209" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A209" s="9"/>
+      <c r="B209" s="9"/>
+      <c r="C209" s="7"/>
+      <c r="D209" s="7"/>
+    </row>
+    <row r="210" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A210" s="9"/>
+      <c r="B210" s="9"/>
+      <c r="C210" s="7"/>
+      <c r="D210" s="7"/>
+    </row>
+    <row r="211" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A211" s="9"/>
+      <c r="B211" s="9"/>
+      <c r="C211" s="7"/>
+      <c r="D211" s="7"/>
+    </row>
+    <row r="212" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A212" s="9"/>
+      <c r="B212" s="9"/>
+      <c r="C212" s="7"/>
+      <c r="D212" s="7"/>
+    </row>
+    <row r="213" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A213" s="9"/>
+      <c r="B213" s="9"/>
+      <c r="C213" s="7"/>
+      <c r="D213" s="7"/>
+    </row>
+    <row r="214" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A214" s="9"/>
+      <c r="B214" s="9"/>
+      <c r="C214" s="7"/>
+      <c r="D214" s="7"/>
+    </row>
+    <row r="215" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A215" s="9"/>
+      <c r="B215" s="9"/>
+      <c r="C215" s="7"/>
+      <c r="D215" s="7"/>
+    </row>
+    <row r="216" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A216" s="9"/>
+      <c r="B216" s="9"/>
+      <c r="C216" s="7"/>
+      <c r="D216" s="7"/>
+    </row>
+    <row r="217" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A217" s="9"/>
+      <c r="B217" s="9"/>
+      <c r="C217" s="7"/>
+      <c r="D217" s="7"/>
+    </row>
+    <row r="218" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A218" s="9"/>
+      <c r="B218" s="9"/>
+      <c r="C218" s="7"/>
+      <c r="D218" s="7"/>
+    </row>
+    <row r="219" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A219" s="9"/>
+      <c r="B219" s="9"/>
+      <c r="C219" s="7"/>
+      <c r="D219" s="7"/>
+    </row>
+    <row r="220" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A220" s="9"/>
+      <c r="B220" s="9"/>
+      <c r="C220" s="7"/>
+      <c r="D220" s="7"/>
+    </row>
+    <row r="221" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A221" s="9"/>
+      <c r="B221" s="9"/>
+      <c r="C221" s="7"/>
+      <c r="D221" s="7"/>
+    </row>
+    <row r="222" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A222" s="9"/>
+      <c r="B222" s="9"/>
+      <c r="C222" s="7"/>
+      <c r="D222" s="7"/>
+    </row>
+    <row r="223" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A223" s="9"/>
+      <c r="B223" s="9"/>
+      <c r="C223" s="7"/>
+      <c r="D223" s="7"/>
+    </row>
+    <row r="224" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A224" s="9"/>
+      <c r="B224" s="9"/>
+      <c r="C224" s="7"/>
+      <c r="D224" s="7"/>
+    </row>
+    <row r="225" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A225" s="9"/>
+      <c r="B225" s="9"/>
+      <c r="C225" s="7"/>
+      <c r="D225" s="7"/>
+    </row>
+    <row r="226" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A226" s="9"/>
+      <c r="B226" s="9"/>
+      <c r="C226" s="7"/>
+      <c r="D226" s="7"/>
+    </row>
+    <row r="227" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A227" s="9"/>
+      <c r="B227" s="9"/>
+      <c r="C227" s="7"/>
+      <c r="D227" s="7"/>
+    </row>
+    <row r="228" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A228" s="9"/>
+      <c r="B228" s="9"/>
+      <c r="C228" s="7"/>
+      <c r="D228" s="7"/>
+    </row>
+    <row r="229" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A229" s="9"/>
+      <c r="B229" s="9"/>
+      <c r="C229" s="7"/>
+      <c r="D229" s="7"/>
+    </row>
+    <row r="230" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A230" s="9"/>
+      <c r="B230" s="9"/>
+      <c r="C230" s="7"/>
+      <c r="D230" s="7"/>
+    </row>
+    <row r="231" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A231" s="9"/>
+      <c r="B231" s="9"/>
+      <c r="C231" s="7"/>
+      <c r="D231" s="7"/>
+    </row>
+    <row r="232" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A232" s="9"/>
+      <c r="B232" s="9"/>
+      <c r="C232" s="7"/>
+      <c r="D232" s="7"/>
+    </row>
+    <row r="233" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A233" s="9"/>
+      <c r="B233" s="9"/>
+      <c r="C233" s="7"/>
+      <c r="D233" s="7"/>
+    </row>
+    <row r="234" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A234" s="9"/>
+      <c r="B234" s="9"/>
+      <c r="C234" s="7"/>
+      <c r="D234" s="7"/>
+    </row>
+    <row r="235" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A235" s="9"/>
+      <c r="B235" s="9"/>
+      <c r="C235" s="7"/>
+      <c r="D235" s="7"/>
+    </row>
+    <row r="236" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A236" s="9"/>
+      <c r="B236" s="9"/>
+      <c r="C236" s="7"/>
+      <c r="D236" s="7"/>
+    </row>
+    <row r="237" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A237" s="9"/>
+      <c r="B237" s="9"/>
+      <c r="C237" s="7"/>
+      <c r="D237" s="7"/>
+    </row>
+    <row r="238" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A238" s="9"/>
+      <c r="B238" s="9"/>
+      <c r="C238" s="7"/>
+      <c r="D238" s="7"/>
+    </row>
+    <row r="239" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A239" s="9"/>
+      <c r="B239" s="9"/>
+      <c r="C239" s="7"/>
+      <c r="D239" s="7"/>
+    </row>
+    <row r="240" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A240" s="9"/>
+      <c r="B240" s="9"/>
+      <c r="C240" s="7"/>
+      <c r="D240" s="7"/>
+    </row>
+    <row r="241" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A241" s="9"/>
+      <c r="B241" s="9"/>
+      <c r="C241" s="7"/>
+      <c r="D241" s="7"/>
+    </row>
+    <row r="242" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A242" s="9"/>
+      <c r="B242" s="9"/>
+      <c r="C242" s="7"/>
+      <c r="D242" s="7"/>
+    </row>
+    <row r="243" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A243" s="9"/>
+      <c r="B243" s="9"/>
+      <c r="C243" s="7"/>
+      <c r="D243" s="7"/>
+    </row>
+    <row r="244" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A244" s="9"/>
+      <c r="B244" s="9"/>
+      <c r="C244" s="7"/>
+      <c r="D244" s="7"/>
+    </row>
+    <row r="245" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A245" s="9"/>
+      <c r="B245" s="9"/>
+      <c r="C245" s="7"/>
+      <c r="D245" s="7"/>
+    </row>
+    <row r="246" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A246" s="9"/>
+      <c r="B246" s="9"/>
+      <c r="C246" s="7"/>
+      <c r="D246" s="7"/>
+    </row>
+    <row r="247" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A247" s="9"/>
+      <c r="B247" s="9"/>
+      <c r="C247" s="7"/>
+      <c r="D247" s="7"/>
+    </row>
+    <row r="248" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A248" s="9"/>
+      <c r="B248" s="9"/>
+      <c r="C248" s="7"/>
+      <c r="D248" s="7"/>
+    </row>
+    <row r="249" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A249" s="9"/>
+      <c r="B249" s="9"/>
+      <c r="C249" s="7"/>
+      <c r="D249" s="7"/>
+    </row>
+    <row r="250" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A250" s="9"/>
+      <c r="B250" s="9"/>
+      <c r="C250" s="7"/>
+      <c r="D250" s="7"/>
+    </row>
+    <row r="251" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A251" s="9"/>
+      <c r="B251" s="9"/>
+      <c r="C251" s="7"/>
+      <c r="D251" s="7"/>
+    </row>
+    <row r="252" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A252" s="9"/>
+      <c r="B252" s="9"/>
+      <c r="C252" s="7"/>
+      <c r="D252" s="7"/>
+    </row>
+    <row r="253" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A253" s="9"/>
+      <c r="B253" s="9"/>
+      <c r="C253" s="7"/>
+      <c r="D253" s="7"/>
+    </row>
+    <row r="254" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A254" s="9"/>
+      <c r="B254" s="9"/>
+      <c r="C254" s="7"/>
+      <c r="D254" s="7"/>
+    </row>
+    <row r="255" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A255" s="9"/>
+      <c r="B255" s="9"/>
+      <c r="C255" s="7"/>
+      <c r="D255" s="7"/>
+    </row>
+    <row r="256" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A256" s="9"/>
+      <c r="B256" s="9"/>
+      <c r="C256" s="7"/>
+      <c r="D256" s="7"/>
+    </row>
+    <row r="257" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A257" s="9"/>
+      <c r="B257" s="9"/>
+      <c r="C257" s="7"/>
+      <c r="D257" s="7"/>
+    </row>
+    <row r="258" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A258" s="9"/>
+      <c r="B258" s="9"/>
+      <c r="C258" s="7"/>
+      <c r="D258" s="7"/>
+    </row>
+    <row r="259" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A259" s="9"/>
+      <c r="B259" s="9"/>
+      <c r="C259" s="7"/>
+      <c r="D259" s="7"/>
+    </row>
+    <row r="260" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A260" s="9"/>
+      <c r="B260" s="9"/>
+      <c r="C260" s="7"/>
+      <c r="D260" s="7"/>
+    </row>
+    <row r="261" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A261" s="9"/>
+      <c r="B261" s="9"/>
+      <c r="C261" s="7"/>
+      <c r="D261" s="7"/>
+    </row>
+    <row r="262" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A262" s="9"/>
+      <c r="B262" s="9"/>
+      <c r="C262" s="7"/>
+      <c r="D262" s="7"/>
+    </row>
+    <row r="263" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A263" s="9"/>
+      <c r="B263" s="9"/>
+      <c r="C263" s="7"/>
+      <c r="D263" s="7"/>
+    </row>
+    <row r="264" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A264" s="9"/>
+      <c r="B264" s="9"/>
+      <c r="C264" s="7"/>
+      <c r="D264" s="7"/>
+    </row>
+    <row r="265" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A265" s="9"/>
+      <c r="B265" s="9"/>
+      <c r="C265" s="7"/>
+      <c r="D265" s="7"/>
+    </row>
+    <row r="266" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A266" s="9"/>
+      <c r="B266" s="9"/>
+      <c r="C266" s="7"/>
+      <c r="D266" s="7"/>
+    </row>
+    <row r="267" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A267" s="9"/>
+      <c r="B267" s="9"/>
+      <c r="C267" s="7"/>
+      <c r="D267" s="7"/>
+    </row>
+    <row r="268" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A268" s="9"/>
+      <c r="B268" s="9"/>
+      <c r="C268" s="7"/>
+      <c r="D268" s="7"/>
+    </row>
+    <row r="269" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A269" s="9"/>
+      <c r="B269" s="9"/>
+      <c r="C269" s="7"/>
+      <c r="D269" s="7"/>
+    </row>
+    <row r="270" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A270" s="9"/>
+      <c r="B270" s="9"/>
+      <c r="C270" s="7"/>
+      <c r="D270" s="7"/>
+    </row>
+    <row r="271" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A271" s="9"/>
+      <c r="B271" s="9"/>
+      <c r="C271" s="7"/>
+      <c r="D271" s="7"/>
+    </row>
+    <row r="272" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A272" s="9"/>
+      <c r="B272" s="9"/>
+      <c r="C272" s="7"/>
+      <c r="D272" s="7"/>
+    </row>
+    <row r="273" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A273" s="9"/>
+      <c r="B273" s="9"/>
+      <c r="C273" s="7"/>
+      <c r="D273" s="7"/>
+    </row>
+    <row r="274" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A274" s="9"/>
+      <c r="B274" s="9"/>
+      <c r="C274" s="7"/>
+      <c r="D274" s="7"/>
+    </row>
+    <row r="275" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A275" s="9"/>
+      <c r="B275" s="9"/>
+      <c r="C275" s="7"/>
+      <c r="D275" s="7"/>
+    </row>
+    <row r="276" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A276" s="9"/>
+      <c r="B276" s="9"/>
+      <c r="C276" s="7"/>
+      <c r="D276" s="7"/>
+    </row>
+    <row r="277" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A277" s="9"/>
+      <c r="B277" s="9"/>
+      <c r="C277" s="7"/>
+      <c r="D277" s="7"/>
+    </row>
+    <row r="278" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A278" s="9"/>
+      <c r="B278" s="9"/>
+      <c r="C278" s="7"/>
+      <c r="D278" s="7"/>
+    </row>
+    <row r="279" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A279" s="9"/>
+      <c r="B279" s="9"/>
+      <c r="C279" s="7"/>
+      <c r="D279" s="7"/>
+    </row>
+    <row r="280" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A280" s="9"/>
+      <c r="B280" s="9"/>
+      <c r="C280" s="7"/>
+      <c r="D280" s="7"/>
+    </row>
+    <row r="281" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A281" s="9"/>
+      <c r="B281" s="9"/>
+      <c r="C281" s="7"/>
+      <c r="D281" s="7"/>
+    </row>
+    <row r="282" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A282" s="9"/>
+      <c r="B282" s="9"/>
+      <c r="C282" s="7"/>
+      <c r="D282" s="7"/>
+    </row>
+    <row r="283" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A283" s="9"/>
+      <c r="B283" s="9"/>
+      <c r="C283" s="7"/>
+      <c r="D283" s="7"/>
+    </row>
+    <row r="284" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A284" s="9"/>
+      <c r="B284" s="9"/>
+      <c r="C284" s="7"/>
+      <c r="D284" s="7"/>
+    </row>
+    <row r="285" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A285" s="9"/>
+      <c r="B285" s="9"/>
+      <c r="C285" s="7"/>
+      <c r="D285" s="7"/>
+    </row>
+    <row r="286" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A286" s="9"/>
+      <c r="B286" s="9"/>
+      <c r="C286" s="7"/>
+      <c r="D286" s="7"/>
+    </row>
+    <row r="287" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A287" s="9"/>
+      <c r="B287" s="9"/>
+      <c r="C287" s="7"/>
+      <c r="D287" s="7"/>
+    </row>
+    <row r="288" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A288" s="9"/>
+      <c r="B288" s="9"/>
+      <c r="C288" s="7"/>
+      <c r="D288" s="7"/>
+    </row>
+    <row r="289" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A289" s="9"/>
+      <c r="B289" s="9"/>
+      <c r="C289" s="7"/>
+      <c r="D289" s="7"/>
+    </row>
+    <row r="290" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A290" s="9"/>
+      <c r="B290" s="9"/>
+      <c r="C290" s="7"/>
+      <c r="D290" s="7"/>
+    </row>
+    <row r="291" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A291" s="9"/>
+      <c r="B291" s="9"/>
+      <c r="C291" s="7"/>
+      <c r="D291" s="7"/>
+    </row>
+    <row r="292" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A292" s="9"/>
+      <c r="B292" s="9"/>
+      <c r="C292" s="7"/>
+      <c r="D292" s="7"/>
+    </row>
+    <row r="293" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A293" s="9"/>
+      <c r="B293" s="9"/>
+      <c r="C293" s="7"/>
+      <c r="D293" s="7"/>
+    </row>
+    <row r="294" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A294" s="9"/>
+      <c r="B294" s="9"/>
+      <c r="C294" s="7"/>
+      <c r="D294" s="7"/>
+    </row>
+    <row r="295" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A295" s="9"/>
+      <c r="B295" s="9"/>
+      <c r="C295" s="7"/>
+      <c r="D295" s="7"/>
+    </row>
+    <row r="296" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A296" s="9"/>
+      <c r="B296" s="9"/>
+      <c r="C296" s="7"/>
+      <c r="D296" s="7"/>
+    </row>
+    <row r="297" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A297" s="9"/>
+      <c r="B297" s="9"/>
+      <c r="C297" s="7"/>
+      <c r="D297" s="7"/>
+    </row>
+    <row r="298" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A298" s="9"/>
+      <c r="B298" s="9"/>
+      <c r="C298" s="7"/>
+      <c r="D298" s="7"/>
+    </row>
+    <row r="299" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A299" s="9"/>
+      <c r="B299" s="9"/>
+      <c r="C299" s="7"/>
+      <c r="D299" s="7"/>
+    </row>
+    <row r="300" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A300" s="9"/>
+      <c r="B300" s="9"/>
+      <c r="C300" s="7"/>
+      <c r="D300" s="7"/>
+    </row>
+    <row r="301" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A301" s="9"/>
+      <c r="B301" s="9"/>
+      <c r="C301" s="7"/>
+      <c r="D301" s="7"/>
+    </row>
+    <row r="302" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A302" s="9"/>
+      <c r="B302" s="9"/>
+      <c r="C302" s="7"/>
+      <c r="D302" s="7"/>
+    </row>
+    <row r="303" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A303" s="9"/>
+      <c r="B303" s="9"/>
+      <c r="C303" s="7"/>
+      <c r="D303" s="7"/>
+    </row>
+    <row r="304" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A304" s="9"/>
+      <c r="B304" s="9"/>
+      <c r="C304" s="7"/>
+      <c r="D304" s="7"/>
+    </row>
+    <row r="305" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A305" s="9"/>
+      <c r="B305" s="9"/>
+      <c r="C305" s="7"/>
+      <c r="D305" s="7"/>
+    </row>
+    <row r="306" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A306" s="9"/>
+      <c r="B306" s="9"/>
+      <c r="C306" s="7"/>
+      <c r="D306" s="7"/>
+    </row>
+    <row r="307" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A307" s="9"/>
+      <c r="B307" s="9"/>
+      <c r="C307" s="7"/>
+      <c r="D307" s="7"/>
+    </row>
+    <row r="308" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A308" s="9"/>
+      <c r="B308" s="9"/>
+      <c r="C308" s="7"/>
+      <c r="D308" s="7"/>
+    </row>
+    <row r="309" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A309" s="9"/>
+      <c r="B309" s="9"/>
+      <c r="C309" s="7"/>
+      <c r="D309" s="7"/>
+    </row>
+    <row r="310" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A310" s="9"/>
+      <c r="B310" s="9"/>
+      <c r="C310" s="7"/>
+      <c r="D310" s="7"/>
+    </row>
+    <row r="311" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A311" s="9"/>
+      <c r="B311" s="9"/>
+      <c r="C311" s="7"/>
+      <c r="D311" s="7"/>
+    </row>
+    <row r="312" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A312" s="9"/>
+      <c r="B312" s="9"/>
+      <c r="C312" s="7"/>
+      <c r="D312" s="7"/>
+    </row>
+    <row r="313" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A313" s="9"/>
+      <c r="B313" s="9"/>
+      <c r="C313" s="7"/>
+      <c r="D313" s="7"/>
+    </row>
+    <row r="314" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A314" s="9"/>
+      <c r="B314" s="9"/>
+      <c r="C314" s="7"/>
+      <c r="D314" s="7"/>
+    </row>
+    <row r="315" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A315" s="9"/>
+      <c r="B315" s="9"/>
+      <c r="C315" s="7"/>
+      <c r="D315" s="7"/>
+    </row>
+    <row r="316" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A316" s="9"/>
+      <c r="B316" s="9"/>
+      <c r="C316" s="7"/>
+      <c r="D316" s="7"/>
+    </row>
+    <row r="317" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A317" s="9"/>
+      <c r="B317" s="9"/>
+      <c r="C317" s="7"/>
+      <c r="D317" s="7"/>
+    </row>
+    <row r="318" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A318" s="9"/>
+      <c r="B318" s="9"/>
+      <c r="C318" s="7"/>
+      <c r="D318" s="7"/>
+    </row>
+    <row r="319" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A319" s="9"/>
+      <c r="B319" s="9"/>
+      <c r="C319" s="7"/>
+      <c r="D319" s="7"/>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A320" s="7"/>
+      <c r="B320" s="7"/>
+      <c r="C320" s="7"/>
+      <c r="D320" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/m2.xlsx
+++ b/m2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\سعيات\م2 - ف2\steam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C2B636-328C-458A-B629-72D0A5E910C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADAEAF2-928D-4DF1-ACB3-0C692772A8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -516,7 +516,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -527,19 +527,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -821,7 +819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E830AE-5C32-4A25-A5BE-EAB4941C3B09}">
-  <dimension ref="A1:P320"/>
+  <dimension ref="A1:P319"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
@@ -843,44 +841,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="7"/>
+      <c r="E1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6" t="s">
+      <c r="F1" s="7"/>
+      <c r="G1" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6" t="s">
+      <c r="H1" s="7"/>
+      <c r="I1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6" t="s">
+      <c r="J1" s="7"/>
+      <c r="K1" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6" t="s">
+      <c r="L1" s="7"/>
+      <c r="M1" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6" t="s">
+      <c r="N1" s="7"/>
+      <c r="O1" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="P1" s="6"/>
+      <c r="P1" s="7"/>
     </row>
     <row r="2" spans="1:16" ht="21" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
@@ -961,10 +959,18 @@
       <c r="L3" s="2">
         <v>1</v>
       </c>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
+      <c r="M3" s="2">
+        <v>21</v>
+      </c>
+      <c r="N3" s="2">
+        <v>4</v>
+      </c>
+      <c r="O3" s="2">
+        <v>20</v>
+      </c>
+      <c r="P3" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="4" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
@@ -1003,10 +1009,18 @@
       <c r="L4" s="2">
         <v>2</v>
       </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
+      <c r="M4" s="2">
+        <v>26</v>
+      </c>
+      <c r="N4" s="2">
+        <v>5</v>
+      </c>
+      <c r="O4" s="2">
+        <v>27</v>
+      </c>
+      <c r="P4" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="5" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
@@ -1045,10 +1059,18 @@
       <c r="L5" s="2">
         <v>4</v>
       </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
+      <c r="M5" s="2">
+        <v>29</v>
+      </c>
+      <c r="N5" s="2">
+        <v>4</v>
+      </c>
+      <c r="O5" s="2">
+        <v>24</v>
+      </c>
+      <c r="P5" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="6" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
@@ -1087,10 +1109,18 @@
       <c r="L6" s="2">
         <v>8</v>
       </c>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
+      <c r="M6" s="2">
+        <v>31</v>
+      </c>
+      <c r="N6" s="2">
+        <v>7</v>
+      </c>
+      <c r="O6" s="2">
+        <v>31</v>
+      </c>
+      <c r="P6" s="2">
+        <v>8</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
@@ -1129,10 +1159,18 @@
       <c r="L7" s="2">
         <v>5</v>
       </c>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
+      <c r="M7" s="2">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2">
+        <v>4</v>
+      </c>
+      <c r="O7" s="2">
+        <v>20</v>
+      </c>
+      <c r="P7" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="8" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A8" s="3">
@@ -1171,10 +1209,18 @@
       <c r="L8" s="2">
         <v>8</v>
       </c>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
+      <c r="M8" s="2">
+        <v>36</v>
+      </c>
+      <c r="N8" s="2">
+        <v>10</v>
+      </c>
+      <c r="O8" s="2">
+        <v>39</v>
+      </c>
+      <c r="P8" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A9" s="3">
@@ -1213,10 +1259,18 @@
       <c r="L9" s="2">
         <v>6</v>
       </c>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
+      <c r="M9" s="2">
+        <v>36</v>
+      </c>
+      <c r="N9" s="2">
+        <v>10</v>
+      </c>
+      <c r="O9" s="2">
+        <v>39</v>
+      </c>
+      <c r="P9" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A10" s="3">
@@ -1255,10 +1309,18 @@
       <c r="L10" s="2">
         <v>8</v>
       </c>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
+      <c r="M10" s="2">
+        <v>24</v>
+      </c>
+      <c r="N10" s="2">
+        <v>4</v>
+      </c>
+      <c r="O10" s="2">
+        <v>24</v>
+      </c>
+      <c r="P10" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="11" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A11" s="3">
@@ -1297,10 +1359,18 @@
       <c r="L11" s="2">
         <v>8</v>
       </c>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
+      <c r="M11" s="2">
+        <v>23</v>
+      </c>
+      <c r="N11" s="2">
+        <v>5</v>
+      </c>
+      <c r="O11" s="2">
+        <v>23</v>
+      </c>
+      <c r="P11" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="12" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A12" s="3">
@@ -1339,10 +1409,18 @@
       <c r="L12" s="2">
         <v>2</v>
       </c>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
+      <c r="M12" s="2">
+        <v>18</v>
+      </c>
+      <c r="N12" s="2">
+        <v>5</v>
+      </c>
+      <c r="O12" s="2">
+        <v>24</v>
+      </c>
+      <c r="P12" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A13" s="3">
@@ -1381,10 +1459,18 @@
       <c r="L13" s="2">
         <v>10</v>
       </c>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
+      <c r="M13" s="2">
+        <v>25</v>
+      </c>
+      <c r="N13" s="2">
+        <v>6</v>
+      </c>
+      <c r="O13" s="2">
+        <v>26</v>
+      </c>
+      <c r="P13" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="14" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A14" s="3">
@@ -1423,10 +1509,18 @@
       <c r="L14" s="2">
         <v>5</v>
       </c>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
+      <c r="M14" s="2">
+        <v>29</v>
+      </c>
+      <c r="N14" s="2">
+        <v>6</v>
+      </c>
+      <c r="O14" s="2">
+        <v>28</v>
+      </c>
+      <c r="P14" s="2">
+        <v>8</v>
+      </c>
     </row>
     <row r="15" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A15" s="3">
@@ -1465,10 +1559,18 @@
       <c r="L15" s="2">
         <v>6</v>
       </c>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
+      <c r="M15" s="2">
+        <v>31</v>
+      </c>
+      <c r="N15" s="2">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2">
+        <v>35</v>
+      </c>
+      <c r="P15" s="2">
+        <v>8</v>
+      </c>
     </row>
     <row r="16" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A16" s="3">
@@ -1507,10 +1609,18 @@
       <c r="L16" s="2">
         <v>6</v>
       </c>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
+      <c r="M16" s="2">
+        <v>24</v>
+      </c>
+      <c r="N16" s="2">
+        <v>4</v>
+      </c>
+      <c r="O16" s="2">
+        <v>24</v>
+      </c>
+      <c r="P16" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="17" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A17" s="3">
@@ -1549,10 +1659,18 @@
       <c r="L17" s="2">
         <v>6</v>
       </c>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
+      <c r="M17" s="2">
+        <v>25</v>
+      </c>
+      <c r="N17" s="2">
+        <v>5</v>
+      </c>
+      <c r="O17" s="2">
+        <v>25</v>
+      </c>
+      <c r="P17" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="18" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A18" s="3">
@@ -1574,7 +1692,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H18" s="2">
         <v>0</v>
@@ -1586,13 +1704,23 @@
         <v>7</v>
       </c>
       <c r="K18" s="2">
+        <v>14</v>
+      </c>
+      <c r="L18" s="2">
         <v>0</v>
       </c>
-      <c r="L18" s="2"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
+      <c r="M18" s="2">
+        <v>14</v>
+      </c>
+      <c r="N18" s="2">
+        <v>0</v>
+      </c>
+      <c r="O18" s="2">
+        <v>0</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A19" s="3">
@@ -1631,10 +1759,18 @@
       <c r="L19" s="2">
         <v>6</v>
       </c>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
+      <c r="M19" s="2">
+        <v>33</v>
+      </c>
+      <c r="N19" s="2">
+        <v>9</v>
+      </c>
+      <c r="O19" s="2">
+        <v>36</v>
+      </c>
+      <c r="P19" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="20" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A20" s="3">
@@ -1673,10 +1809,18 @@
       <c r="L20" s="2">
         <v>8</v>
       </c>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
+      <c r="M20" s="2">
+        <v>26</v>
+      </c>
+      <c r="N20" s="2">
+        <v>5</v>
+      </c>
+      <c r="O20" s="2">
+        <v>26</v>
+      </c>
+      <c r="P20" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="21" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="3">
@@ -1715,10 +1859,18 @@
       <c r="L21" s="2">
         <v>4</v>
       </c>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
+      <c r="M21" s="2">
+        <v>25</v>
+      </c>
+      <c r="N21" s="2">
+        <v>5</v>
+      </c>
+      <c r="O21" s="2">
+        <v>25</v>
+      </c>
+      <c r="P21" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="22" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A22" s="3">
@@ -1757,10 +1909,18 @@
       <c r="L22" s="2">
         <v>4</v>
       </c>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
+      <c r="M22" s="2">
+        <v>26</v>
+      </c>
+      <c r="N22" s="2">
+        <v>5</v>
+      </c>
+      <c r="O22" s="2">
+        <v>26</v>
+      </c>
+      <c r="P22" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="23" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A23" s="3">
@@ -1799,10 +1959,18 @@
       <c r="L23" s="2">
         <v>2</v>
       </c>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
+      <c r="M23" s="2">
+        <v>22</v>
+      </c>
+      <c r="N23" s="2">
+        <v>5</v>
+      </c>
+      <c r="O23" s="2">
+        <v>24</v>
+      </c>
+      <c r="P23" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="24" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A24" s="3">
@@ -1841,10 +2009,18 @@
       <c r="L24" s="2">
         <v>6</v>
       </c>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
+      <c r="M24" s="2">
+        <v>28</v>
+      </c>
+      <c r="N24" s="2">
+        <v>6</v>
+      </c>
+      <c r="O24" s="2">
+        <v>29</v>
+      </c>
+      <c r="P24" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="25" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A25" s="3">
@@ -1883,10 +2059,18 @@
       <c r="L25" s="2">
         <v>6</v>
       </c>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
+      <c r="M25" s="2">
+        <v>23</v>
+      </c>
+      <c r="N25" s="2">
+        <v>5</v>
+      </c>
+      <c r="O25" s="2">
+        <v>25</v>
+      </c>
+      <c r="P25" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="26" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A26" s="3">
@@ -1925,10 +2109,18 @@
       <c r="L26" s="2">
         <v>2</v>
       </c>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
+      <c r="M26" s="2">
+        <v>23</v>
+      </c>
+      <c r="N26" s="2">
+        <v>4</v>
+      </c>
+      <c r="O26" s="2">
+        <v>23</v>
+      </c>
+      <c r="P26" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="27" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A27" s="3">
@@ -1967,10 +2159,18 @@
       <c r="L27" s="2">
         <v>2</v>
       </c>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
+      <c r="M27" s="2">
+        <v>27</v>
+      </c>
+      <c r="N27" s="2">
+        <v>8</v>
+      </c>
+      <c r="O27" s="2">
+        <v>34</v>
+      </c>
+      <c r="P27" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="28" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A28" s="3">
@@ -2009,10 +2209,18 @@
       <c r="L28" s="2">
         <v>8</v>
       </c>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
+      <c r="M28" s="2">
+        <v>27</v>
+      </c>
+      <c r="N28" s="2">
+        <v>6</v>
+      </c>
+      <c r="O28" s="2">
+        <v>28</v>
+      </c>
+      <c r="P28" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="29" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A29" s="3">
@@ -2048,11 +2256,21 @@
       <c r="K29" s="2">
         <v>0</v>
       </c>
-      <c r="L29" s="2"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
+      <c r="L29" s="2">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2">
+        <v>0</v>
+      </c>
+      <c r="N29" s="2">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2">
+        <v>0</v>
+      </c>
+      <c r="P29" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A30" s="3">
@@ -2091,10 +2309,18 @@
       <c r="L30" s="2">
         <v>10</v>
       </c>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
+      <c r="M30" s="2">
+        <v>34</v>
+      </c>
+      <c r="N30" s="2">
+        <v>9</v>
+      </c>
+      <c r="O30" s="2">
+        <v>37</v>
+      </c>
+      <c r="P30" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="31" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A31" s="3">
@@ -2133,10 +2359,18 @@
       <c r="L31" s="2">
         <v>4</v>
       </c>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
+      <c r="M31" s="2">
+        <v>28</v>
+      </c>
+      <c r="N31" s="2">
+        <v>6</v>
+      </c>
+      <c r="O31" s="2">
+        <v>28</v>
+      </c>
+      <c r="P31" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="32" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A32" s="3">
@@ -2175,10 +2409,18 @@
       <c r="L32" s="2">
         <v>2</v>
       </c>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5"/>
-      <c r="P32" s="5"/>
+      <c r="M32" s="2">
+        <v>18</v>
+      </c>
+      <c r="N32" s="2">
+        <v>3</v>
+      </c>
+      <c r="O32" s="2">
+        <v>15</v>
+      </c>
+      <c r="P32" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="33" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A33" s="3">
@@ -2217,10 +2459,18 @@
       <c r="L33" s="2">
         <v>2</v>
       </c>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
+      <c r="M33" s="2">
+        <v>30</v>
+      </c>
+      <c r="N33" s="2">
+        <v>8</v>
+      </c>
+      <c r="O33" s="2">
+        <v>35</v>
+      </c>
+      <c r="P33" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="34" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A34" s="3">
@@ -2259,10 +2509,18 @@
       <c r="L34" s="2">
         <v>1</v>
       </c>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
+      <c r="M34" s="2">
+        <v>30</v>
+      </c>
+      <c r="N34" s="2">
+        <v>7</v>
+      </c>
+      <c r="O34" s="2">
+        <v>32</v>
+      </c>
+      <c r="P34" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="35" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A35" s="3">
@@ -2301,10 +2559,18 @@
       <c r="L35" s="2">
         <v>2</v>
       </c>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="5"/>
-      <c r="P35" s="5"/>
+      <c r="M35" s="2">
+        <v>24</v>
+      </c>
+      <c r="N35" s="2">
+        <v>4</v>
+      </c>
+      <c r="O35" s="2">
+        <v>23</v>
+      </c>
+      <c r="P35" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="36" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A36" s="3">
@@ -2343,10 +2609,18 @@
       <c r="L36" s="2">
         <v>10</v>
       </c>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
+      <c r="M36" s="2">
+        <v>39</v>
+      </c>
+      <c r="N36" s="2">
+        <v>10</v>
+      </c>
+      <c r="O36" s="2">
+        <v>40</v>
+      </c>
+      <c r="P36" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="37" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A37" s="3">
@@ -2385,10 +2659,18 @@
       <c r="L37" s="2">
         <v>2</v>
       </c>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5"/>
-      <c r="P37" s="5"/>
+      <c r="M37" s="2">
+        <v>24</v>
+      </c>
+      <c r="N37" s="2">
+        <v>6</v>
+      </c>
+      <c r="O37" s="2">
+        <v>28</v>
+      </c>
+      <c r="P37" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="38" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A38" s="3">
@@ -2427,10 +2709,18 @@
       <c r="L38" s="2">
         <v>4</v>
       </c>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
+      <c r="M38" s="2">
+        <v>28</v>
+      </c>
+      <c r="N38" s="2">
+        <v>6</v>
+      </c>
+      <c r="O38" s="2">
+        <v>28</v>
+      </c>
+      <c r="P38" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="39" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A39" s="3">
@@ -2469,10 +2759,18 @@
       <c r="L39" s="2">
         <v>2</v>
       </c>
-      <c r="M39" s="5"/>
-      <c r="N39" s="5"/>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
+      <c r="M39" s="2">
+        <v>21</v>
+      </c>
+      <c r="N39" s="2">
+        <v>4</v>
+      </c>
+      <c r="O39" s="2">
+        <v>21</v>
+      </c>
+      <c r="P39" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="40" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A40" s="3">
@@ -2511,10 +2809,18 @@
       <c r="L40" s="2">
         <v>6</v>
       </c>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5"/>
-      <c r="P40" s="5"/>
+      <c r="M40" s="2">
+        <v>29</v>
+      </c>
+      <c r="N40" s="2">
+        <v>8</v>
+      </c>
+      <c r="O40" s="2">
+        <v>33</v>
+      </c>
+      <c r="P40" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="41" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A41" s="3">
@@ -2553,10 +2859,18 @@
       <c r="L41" s="2">
         <v>1</v>
       </c>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5"/>
-      <c r="P41" s="5"/>
+      <c r="M41" s="2">
+        <v>18</v>
+      </c>
+      <c r="N41" s="2">
+        <v>3</v>
+      </c>
+      <c r="O41" s="2">
+        <v>17</v>
+      </c>
+      <c r="P41" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="42" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A42" s="3">
@@ -2595,10 +2909,18 @@
       <c r="L42" s="2">
         <v>8</v>
       </c>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
+      <c r="M42" s="2">
+        <v>25</v>
+      </c>
+      <c r="N42" s="2">
+        <v>4</v>
+      </c>
+      <c r="O42" s="2">
+        <v>26</v>
+      </c>
+      <c r="P42" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="43" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A43" s="3">
@@ -2637,10 +2959,18 @@
       <c r="L43" s="2">
         <v>6</v>
       </c>
-      <c r="M43" s="5"/>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
+      <c r="M43" s="2">
+        <v>36</v>
+      </c>
+      <c r="N43" s="2">
+        <v>9</v>
+      </c>
+      <c r="O43" s="2">
+        <v>37</v>
+      </c>
+      <c r="P43" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="44" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A44" s="3">
@@ -2679,10 +3009,18 @@
       <c r="L44" s="2">
         <v>8</v>
       </c>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5"/>
-      <c r="P44" s="5"/>
+      <c r="M44" s="2">
+        <v>34</v>
+      </c>
+      <c r="N44" s="2">
+        <v>9</v>
+      </c>
+      <c r="O44" s="2">
+        <v>37</v>
+      </c>
+      <c r="P44" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="45" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A45" s="3">
@@ -2721,10 +3059,18 @@
       <c r="L45" s="2">
         <v>6</v>
       </c>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5"/>
-      <c r="O45" s="5"/>
-      <c r="P45" s="5"/>
+      <c r="M45" s="2">
+        <v>29</v>
+      </c>
+      <c r="N45" s="2">
+        <v>8</v>
+      </c>
+      <c r="O45" s="2">
+        <v>33</v>
+      </c>
+      <c r="P45" s="2">
+        <v>8</v>
+      </c>
     </row>
     <row r="46" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A46" s="3">
@@ -2763,10 +3109,18 @@
       <c r="L46" s="2">
         <v>8</v>
       </c>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
+      <c r="M46" s="2">
+        <v>34</v>
+      </c>
+      <c r="N46" s="2">
+        <v>9</v>
+      </c>
+      <c r="O46" s="2">
+        <v>37</v>
+      </c>
+      <c r="P46" s="2">
+        <v>8</v>
+      </c>
     </row>
     <row r="47" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A47" s="3">
@@ -2805,10 +3159,18 @@
       <c r="L47" s="2">
         <v>6</v>
       </c>
-      <c r="M47" s="5"/>
-      <c r="N47" s="5"/>
-      <c r="O47" s="5"/>
-      <c r="P47" s="5"/>
+      <c r="M47" s="2">
+        <v>26</v>
+      </c>
+      <c r="N47" s="2">
+        <v>7</v>
+      </c>
+      <c r="O47" s="2">
+        <v>28</v>
+      </c>
+      <c r="P47" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="48" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A48" s="3">
@@ -2847,10 +3209,18 @@
       <c r="L48" s="2">
         <v>10</v>
       </c>
-      <c r="M48" s="5"/>
-      <c r="N48" s="5"/>
-      <c r="O48" s="5"/>
-      <c r="P48" s="5"/>
+      <c r="M48" s="2">
+        <v>39</v>
+      </c>
+      <c r="N48" s="2">
+        <v>10</v>
+      </c>
+      <c r="O48" s="2">
+        <v>40</v>
+      </c>
+      <c r="P48" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="49" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A49" s="3">
@@ -2889,10 +3259,18 @@
       <c r="L49" s="2">
         <v>4</v>
       </c>
-      <c r="M49" s="5"/>
-      <c r="N49" s="5"/>
-      <c r="O49" s="5"/>
-      <c r="P49" s="5"/>
+      <c r="M49" s="2">
+        <v>29</v>
+      </c>
+      <c r="N49" s="2">
+        <v>6</v>
+      </c>
+      <c r="O49" s="2">
+        <v>30</v>
+      </c>
+      <c r="P49" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="50" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A50" s="3">
@@ -2931,10 +3309,18 @@
       <c r="L50" s="2">
         <v>4</v>
       </c>
-      <c r="M50" s="5"/>
-      <c r="N50" s="5"/>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
+      <c r="M50" s="2">
+        <v>30</v>
+      </c>
+      <c r="N50" s="2">
+        <v>7</v>
+      </c>
+      <c r="O50" s="2">
+        <v>31</v>
+      </c>
+      <c r="P50" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="51" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A51" s="3">
@@ -2973,10 +3359,18 @@
       <c r="L51" s="2">
         <v>4</v>
       </c>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5"/>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
+      <c r="M51" s="2">
+        <v>32</v>
+      </c>
+      <c r="N51" s="2">
+        <v>8</v>
+      </c>
+      <c r="O51" s="2">
+        <v>34</v>
+      </c>
+      <c r="P51" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="52" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A52" s="3">
@@ -3015,10 +3409,18 @@
       <c r="L52" s="2">
         <v>10</v>
       </c>
-      <c r="M52" s="5"/>
-      <c r="N52" s="5"/>
-      <c r="O52" s="5"/>
-      <c r="P52" s="5"/>
+      <c r="M52" s="2">
+        <v>25</v>
+      </c>
+      <c r="N52" s="2">
+        <v>4</v>
+      </c>
+      <c r="O52" s="2">
+        <v>24</v>
+      </c>
+      <c r="P52" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="53" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A53" s="3">
@@ -3057,10 +3459,18 @@
       <c r="L53" s="2">
         <v>8</v>
       </c>
-      <c r="M53" s="5"/>
-      <c r="N53" s="5"/>
-      <c r="O53" s="5"/>
-      <c r="P53" s="5"/>
+      <c r="M53" s="2">
+        <v>27</v>
+      </c>
+      <c r="N53" s="2">
+        <v>6</v>
+      </c>
+      <c r="O53" s="2">
+        <v>27</v>
+      </c>
+      <c r="P53" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="54" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A54" s="3">
@@ -3099,10 +3509,18 @@
       <c r="L54" s="2">
         <v>1</v>
       </c>
-      <c r="M54" s="5"/>
-      <c r="N54" s="5"/>
-      <c r="O54" s="5"/>
-      <c r="P54" s="5"/>
+      <c r="M54" s="2">
+        <v>25</v>
+      </c>
+      <c r="N54" s="2">
+        <v>3</v>
+      </c>
+      <c r="O54" s="2">
+        <v>20</v>
+      </c>
+      <c r="P54" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="55" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A55" s="3">
@@ -3141,10 +3559,18 @@
       <c r="L55" s="2">
         <v>8</v>
       </c>
-      <c r="M55" s="5"/>
-      <c r="N55" s="5"/>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
+      <c r="M55" s="2">
+        <v>29</v>
+      </c>
+      <c r="N55" s="2">
+        <v>6</v>
+      </c>
+      <c r="O55" s="2">
+        <v>28</v>
+      </c>
+      <c r="P55" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="56" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A56" s="3">
@@ -3183,10 +3609,18 @@
       <c r="L56" s="2">
         <v>3</v>
       </c>
-      <c r="M56" s="5"/>
-      <c r="N56" s="5"/>
-      <c r="O56" s="5"/>
-      <c r="P56" s="5"/>
+      <c r="M56" s="2">
+        <v>23</v>
+      </c>
+      <c r="N56" s="2">
+        <v>4</v>
+      </c>
+      <c r="O56" s="2">
+        <v>23</v>
+      </c>
+      <c r="P56" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="57" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A57" s="3">
@@ -3225,10 +3659,18 @@
       <c r="L57" s="2">
         <v>8</v>
       </c>
-      <c r="M57" s="5"/>
-      <c r="N57" s="5"/>
-      <c r="O57" s="5"/>
-      <c r="P57" s="5"/>
+      <c r="M57" s="2">
+        <v>26</v>
+      </c>
+      <c r="N57" s="2">
+        <v>5</v>
+      </c>
+      <c r="O57" s="2">
+        <v>26</v>
+      </c>
+      <c r="P57" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="58" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A58" s="3">
@@ -3267,10 +3709,18 @@
       <c r="L58" s="2">
         <v>8</v>
       </c>
-      <c r="M58" s="5"/>
-      <c r="N58" s="5"/>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
+      <c r="M58" s="2">
+        <v>23</v>
+      </c>
+      <c r="N58" s="2">
+        <v>4</v>
+      </c>
+      <c r="O58" s="2">
+        <v>23</v>
+      </c>
+      <c r="P58" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="59" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A59" s="3">
@@ -3309,10 +3759,18 @@
       <c r="L59" s="2">
         <v>4</v>
       </c>
-      <c r="M59" s="5"/>
-      <c r="N59" s="5"/>
-      <c r="O59" s="5"/>
-      <c r="P59" s="5"/>
+      <c r="M59" s="2">
+        <v>26</v>
+      </c>
+      <c r="N59" s="2">
+        <v>5</v>
+      </c>
+      <c r="O59" s="2">
+        <v>25</v>
+      </c>
+      <c r="P59" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="60" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A60" s="3">
@@ -3351,10 +3809,18 @@
       <c r="L60" s="2">
         <v>2</v>
       </c>
-      <c r="M60" s="5"/>
-      <c r="N60" s="5"/>
-      <c r="O60" s="5"/>
-      <c r="P60" s="5"/>
+      <c r="M60" s="2">
+        <v>26</v>
+      </c>
+      <c r="N60" s="2">
+        <v>5</v>
+      </c>
+      <c r="O60" s="2">
+        <v>25</v>
+      </c>
+      <c r="P60" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="61" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A61" s="3">
@@ -3393,10 +3859,18 @@
       <c r="L61" s="2">
         <v>1</v>
       </c>
-      <c r="M61" s="5"/>
-      <c r="N61" s="5"/>
-      <c r="O61" s="5"/>
-      <c r="P61" s="5"/>
+      <c r="M61" s="2">
+        <v>23</v>
+      </c>
+      <c r="N61" s="2">
+        <v>4</v>
+      </c>
+      <c r="O61" s="2">
+        <v>22</v>
+      </c>
+      <c r="P61" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="62" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A62" s="3">
@@ -3435,10 +3909,18 @@
       <c r="L62" s="2">
         <v>2</v>
       </c>
-      <c r="M62" s="5"/>
-      <c r="N62" s="5"/>
-      <c r="O62" s="5"/>
-      <c r="P62" s="5"/>
+      <c r="M62" s="2">
+        <v>18</v>
+      </c>
+      <c r="N62" s="2">
+        <v>3</v>
+      </c>
+      <c r="O62" s="2">
+        <v>20</v>
+      </c>
+      <c r="P62" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="63" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A63" s="3">
@@ -3477,10 +3959,18 @@
       <c r="L63" s="2">
         <v>2</v>
       </c>
-      <c r="M63" s="5"/>
-      <c r="N63" s="5"/>
-      <c r="O63" s="5"/>
-      <c r="P63" s="5"/>
+      <c r="M63" s="2">
+        <v>29</v>
+      </c>
+      <c r="N63" s="2">
+        <v>6</v>
+      </c>
+      <c r="O63" s="2">
+        <v>29</v>
+      </c>
+      <c r="P63" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="64" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A64" s="3">
@@ -3519,10 +4009,18 @@
       <c r="L64" s="2">
         <v>2</v>
       </c>
-      <c r="M64" s="5"/>
-      <c r="N64" s="5"/>
-      <c r="O64" s="5"/>
-      <c r="P64" s="5"/>
+      <c r="M64" s="2">
+        <v>25</v>
+      </c>
+      <c r="N64" s="2">
+        <v>5</v>
+      </c>
+      <c r="O64" s="2">
+        <v>24</v>
+      </c>
+      <c r="P64" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="65" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A65" s="3">
@@ -3561,10 +4059,18 @@
       <c r="L65" s="2">
         <v>8</v>
       </c>
-      <c r="M65" s="5"/>
-      <c r="N65" s="5"/>
-      <c r="O65" s="5"/>
-      <c r="P65" s="5"/>
+      <c r="M65" s="2">
+        <v>27</v>
+      </c>
+      <c r="N65" s="2">
+        <v>5</v>
+      </c>
+      <c r="O65" s="2">
+        <v>25</v>
+      </c>
+      <c r="P65" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="66" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A66" s="3">
@@ -3603,10 +4109,18 @@
       <c r="L66" s="2">
         <v>8</v>
       </c>
-      <c r="M66" s="5"/>
-      <c r="N66" s="5"/>
-      <c r="O66" s="5"/>
-      <c r="P66" s="5"/>
+      <c r="M66" s="2">
+        <v>35</v>
+      </c>
+      <c r="N66" s="2">
+        <v>10</v>
+      </c>
+      <c r="O66" s="2">
+        <v>40</v>
+      </c>
+      <c r="P66" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="67" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A67" s="3">
@@ -3645,10 +4159,18 @@
       <c r="L67" s="2">
         <v>6</v>
       </c>
-      <c r="M67" s="5"/>
-      <c r="N67" s="5"/>
-      <c r="O67" s="5"/>
-      <c r="P67" s="5"/>
+      <c r="M67" s="2">
+        <v>21</v>
+      </c>
+      <c r="N67" s="2">
+        <v>5</v>
+      </c>
+      <c r="O67" s="2">
+        <v>26</v>
+      </c>
+      <c r="P67" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="68" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A68" s="3">
@@ -3687,10 +4209,18 @@
       <c r="L68" s="2">
         <v>1</v>
       </c>
-      <c r="M68" s="5"/>
-      <c r="N68" s="5"/>
-      <c r="O68" s="5"/>
-      <c r="P68" s="5"/>
+      <c r="M68" s="2">
+        <v>23</v>
+      </c>
+      <c r="N68" s="2">
+        <v>5</v>
+      </c>
+      <c r="O68" s="2">
+        <v>25</v>
+      </c>
+      <c r="P68" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="69" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A69" s="3">
@@ -3729,10 +4259,18 @@
       <c r="L69" s="2">
         <v>8</v>
       </c>
-      <c r="M69" s="5"/>
-      <c r="N69" s="5"/>
-      <c r="O69" s="5"/>
-      <c r="P69" s="5"/>
+      <c r="M69" s="2">
+        <v>27</v>
+      </c>
+      <c r="N69" s="2">
+        <v>6</v>
+      </c>
+      <c r="O69" s="2">
+        <v>29</v>
+      </c>
+      <c r="P69" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="70" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A70" s="3">
@@ -3771,10 +4309,18 @@
       <c r="L70" s="2">
         <v>6</v>
       </c>
-      <c r="M70" s="5"/>
-      <c r="N70" s="5"/>
-      <c r="O70" s="5"/>
-      <c r="P70" s="5"/>
+      <c r="M70" s="2">
+        <v>24</v>
+      </c>
+      <c r="N70" s="2">
+        <v>4</v>
+      </c>
+      <c r="O70" s="2">
+        <v>23</v>
+      </c>
+      <c r="P70" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="71" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A71" s="3">
@@ -3813,10 +4359,18 @@
       <c r="L71" s="2">
         <v>6</v>
       </c>
-      <c r="M71" s="5"/>
-      <c r="N71" s="5"/>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5"/>
+      <c r="M71" s="2">
+        <v>25</v>
+      </c>
+      <c r="N71" s="2">
+        <v>5</v>
+      </c>
+      <c r="O71" s="2">
+        <v>26</v>
+      </c>
+      <c r="P71" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="72" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A72" s="3">
@@ -3855,10 +4409,18 @@
       <c r="L72" s="2">
         <v>8</v>
       </c>
-      <c r="M72" s="5"/>
-      <c r="N72" s="5"/>
-      <c r="O72" s="5"/>
-      <c r="P72" s="5"/>
+      <c r="M72" s="2">
+        <v>25</v>
+      </c>
+      <c r="N72" s="2">
+        <v>5</v>
+      </c>
+      <c r="O72" s="2">
+        <v>25</v>
+      </c>
+      <c r="P72" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="73" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A73" s="3">
@@ -3897,10 +4459,18 @@
       <c r="L73" s="2">
         <v>6</v>
       </c>
-      <c r="M73" s="5"/>
-      <c r="N73" s="5"/>
-      <c r="O73" s="5"/>
-      <c r="P73" s="5"/>
+      <c r="M73" s="2">
+        <v>24</v>
+      </c>
+      <c r="N73" s="2">
+        <v>5</v>
+      </c>
+      <c r="O73" s="2">
+        <v>25</v>
+      </c>
+      <c r="P73" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="74" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A74" s="3">
@@ -3939,10 +4509,18 @@
       <c r="L74" s="2">
         <v>6</v>
       </c>
-      <c r="M74" s="5"/>
-      <c r="N74" s="5"/>
-      <c r="O74" s="5"/>
-      <c r="P74" s="5"/>
+      <c r="M74" s="2">
+        <v>27</v>
+      </c>
+      <c r="N74" s="2">
+        <v>6</v>
+      </c>
+      <c r="O74" s="2">
+        <v>28</v>
+      </c>
+      <c r="P74" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="75" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A75" s="3">
@@ -3961,7 +4539,7 @@
         <v>20</v>
       </c>
       <c r="F75" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
@@ -3976,15 +4554,23 @@
         <v>0</v>
       </c>
       <c r="K75" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L75" s="2">
-        <v>4</v>
-      </c>
-      <c r="M75" s="5"/>
-      <c r="N75" s="5"/>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
+        <v>0</v>
+      </c>
+      <c r="M75" s="2">
+        <v>0</v>
+      </c>
+      <c r="N75" s="2">
+        <v>0</v>
+      </c>
+      <c r="O75" s="2">
+        <v>0</v>
+      </c>
+      <c r="P75" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="76" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A76" s="3">
@@ -4023,10 +4609,18 @@
       <c r="L76" s="2">
         <v>1</v>
       </c>
-      <c r="M76" s="5"/>
-      <c r="N76" s="5"/>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
+      <c r="M76" s="2">
+        <v>22</v>
+      </c>
+      <c r="N76" s="2">
+        <v>4</v>
+      </c>
+      <c r="O76" s="2">
+        <v>21</v>
+      </c>
+      <c r="P76" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="77" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A77" s="3">
@@ -4065,10 +4659,18 @@
       <c r="L77" s="2">
         <v>8</v>
       </c>
-      <c r="M77" s="5"/>
-      <c r="N77" s="5"/>
-      <c r="O77" s="5"/>
-      <c r="P77" s="5"/>
+      <c r="M77" s="2">
+        <v>29</v>
+      </c>
+      <c r="N77" s="2">
+        <v>7</v>
+      </c>
+      <c r="O77" s="2">
+        <v>31</v>
+      </c>
+      <c r="P77" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="78" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A78" s="3">
@@ -4107,10 +4709,18 @@
       <c r="L78" s="2">
         <v>8</v>
       </c>
-      <c r="M78" s="5"/>
-      <c r="N78" s="5"/>
-      <c r="O78" s="5"/>
-      <c r="P78" s="5"/>
+      <c r="M78" s="2">
+        <v>24</v>
+      </c>
+      <c r="N78" s="2">
+        <v>5</v>
+      </c>
+      <c r="O78" s="2">
+        <v>25</v>
+      </c>
+      <c r="P78" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="79" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A79" s="3">
@@ -4149,10 +4759,18 @@
       <c r="L79" s="2">
         <v>2</v>
       </c>
-      <c r="M79" s="5"/>
-      <c r="N79" s="5"/>
-      <c r="O79" s="5"/>
-      <c r="P79" s="5"/>
+      <c r="M79" s="2">
+        <v>24</v>
+      </c>
+      <c r="N79" s="2">
+        <v>5</v>
+      </c>
+      <c r="O79" s="2">
+        <v>24</v>
+      </c>
+      <c r="P79" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="80" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A80" s="3">
@@ -4191,10 +4809,18 @@
       <c r="L80" s="2">
         <v>2</v>
       </c>
-      <c r="M80" s="5"/>
-      <c r="N80" s="5"/>
-      <c r="O80" s="5"/>
-      <c r="P80" s="5"/>
+      <c r="M80" s="2">
+        <v>30</v>
+      </c>
+      <c r="N80" s="2">
+        <v>7</v>
+      </c>
+      <c r="O80" s="2">
+        <v>31</v>
+      </c>
+      <c r="P80" s="2">
+        <v>8</v>
+      </c>
     </row>
     <row r="81" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A81" s="3">
@@ -4233,10 +4859,18 @@
       <c r="L81" s="2">
         <v>4</v>
       </c>
-      <c r="M81" s="5"/>
-      <c r="N81" s="5"/>
-      <c r="O81" s="5"/>
-      <c r="P81" s="5"/>
+      <c r="M81" s="2">
+        <v>26</v>
+      </c>
+      <c r="N81" s="2">
+        <v>5</v>
+      </c>
+      <c r="O81" s="2">
+        <v>25</v>
+      </c>
+      <c r="P81" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="82" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A82" s="3">
@@ -4275,10 +4909,18 @@
       <c r="L82" s="2">
         <v>4</v>
       </c>
-      <c r="M82" s="5"/>
-      <c r="N82" s="5"/>
-      <c r="O82" s="5"/>
-      <c r="P82" s="5"/>
+      <c r="M82" s="2">
+        <v>24</v>
+      </c>
+      <c r="N82" s="2">
+        <v>5</v>
+      </c>
+      <c r="O82" s="2">
+        <v>25</v>
+      </c>
+      <c r="P82" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="83" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A83" s="3">
@@ -4317,10 +4959,18 @@
       <c r="L83" s="2">
         <v>4</v>
       </c>
-      <c r="M83" s="5"/>
-      <c r="N83" s="5"/>
-      <c r="O83" s="5"/>
-      <c r="P83" s="5"/>
+      <c r="M83" s="2">
+        <v>25</v>
+      </c>
+      <c r="N83" s="2">
+        <v>5</v>
+      </c>
+      <c r="O83" s="2">
+        <v>25</v>
+      </c>
+      <c r="P83" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="84" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A84" s="3">
@@ -4359,10 +5009,18 @@
       <c r="L84" s="2">
         <v>10</v>
       </c>
-      <c r="M84" s="5"/>
-      <c r="N84" s="5"/>
-      <c r="O84" s="5"/>
-      <c r="P84" s="5"/>
+      <c r="M84" s="2">
+        <v>39</v>
+      </c>
+      <c r="N84" s="2">
+        <v>10</v>
+      </c>
+      <c r="O84" s="2">
+        <v>40</v>
+      </c>
+      <c r="P84" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="85" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A85" s="3">
@@ -4401,10 +5059,18 @@
       <c r="L85" s="2">
         <v>4</v>
       </c>
-      <c r="M85" s="5"/>
-      <c r="N85" s="5"/>
-      <c r="O85" s="5"/>
-      <c r="P85" s="5"/>
+      <c r="M85" s="2">
+        <v>24</v>
+      </c>
+      <c r="N85" s="2">
+        <v>4</v>
+      </c>
+      <c r="O85" s="2">
+        <v>23</v>
+      </c>
+      <c r="P85" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="86" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A86" s="3">
@@ -4443,10 +5109,18 @@
       <c r="L86" s="2">
         <v>1</v>
       </c>
-      <c r="M86" s="5"/>
-      <c r="N86" s="5"/>
-      <c r="O86" s="5"/>
-      <c r="P86" s="5"/>
+      <c r="M86" s="2">
+        <v>16</v>
+      </c>
+      <c r="N86" s="2">
+        <v>3</v>
+      </c>
+      <c r="O86" s="2">
+        <v>17</v>
+      </c>
+      <c r="P86" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="87" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A87" s="3">
@@ -4485,10 +5159,18 @@
       <c r="L87" s="2">
         <v>8</v>
       </c>
-      <c r="M87" s="5"/>
-      <c r="N87" s="5"/>
-      <c r="O87" s="5"/>
-      <c r="P87" s="5"/>
+      <c r="M87" s="2">
+        <v>33</v>
+      </c>
+      <c r="N87" s="2">
+        <v>8</v>
+      </c>
+      <c r="O87" s="2">
+        <v>33</v>
+      </c>
+      <c r="P87" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="88" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A88" s="3">
@@ -4527,10 +5209,18 @@
       <c r="L88" s="2">
         <v>2</v>
       </c>
-      <c r="M88" s="5"/>
-      <c r="N88" s="5"/>
-      <c r="O88" s="5"/>
-      <c r="P88" s="5"/>
+      <c r="M88" s="2">
+        <v>32</v>
+      </c>
+      <c r="N88" s="2">
+        <v>7</v>
+      </c>
+      <c r="O88" s="2">
+        <v>32</v>
+      </c>
+      <c r="P88" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="89" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A89" s="3">
@@ -4569,10 +5259,18 @@
       <c r="L89" s="2">
         <v>2</v>
       </c>
-      <c r="M89" s="5"/>
-      <c r="N89" s="5"/>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
+      <c r="M89" s="2">
+        <v>33</v>
+      </c>
+      <c r="N89" s="2">
+        <v>10</v>
+      </c>
+      <c r="O89" s="2">
+        <v>38</v>
+      </c>
+      <c r="P89" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="90" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A90" s="3">
@@ -4611,10 +5309,18 @@
       <c r="L90" s="2">
         <v>1</v>
       </c>
-      <c r="M90" s="5"/>
-      <c r="N90" s="5"/>
-      <c r="O90" s="5"/>
-      <c r="P90" s="5"/>
+      <c r="M90" s="2">
+        <v>29</v>
+      </c>
+      <c r="N90" s="2">
+        <v>6</v>
+      </c>
+      <c r="O90" s="2">
+        <v>28</v>
+      </c>
+      <c r="P90" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="91" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A91" s="3">
@@ -4653,10 +5359,18 @@
       <c r="L91" s="2">
         <v>8</v>
       </c>
-      <c r="M91" s="5"/>
-      <c r="N91" s="5"/>
-      <c r="O91" s="5"/>
-      <c r="P91" s="5"/>
+      <c r="M91" s="2">
+        <v>25</v>
+      </c>
+      <c r="N91" s="2">
+        <v>4</v>
+      </c>
+      <c r="O91" s="2">
+        <v>23</v>
+      </c>
+      <c r="P91" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="92" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A92" s="3">
@@ -4695,10 +5409,18 @@
       <c r="L92" s="2">
         <v>1</v>
       </c>
-      <c r="M92" s="5"/>
-      <c r="N92" s="5"/>
-      <c r="O92" s="5"/>
-      <c r="P92" s="5"/>
+      <c r="M92" s="2">
+        <v>22</v>
+      </c>
+      <c r="N92" s="2">
+        <v>4</v>
+      </c>
+      <c r="O92" s="2">
+        <v>22</v>
+      </c>
+      <c r="P92" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="93" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A93" s="3">
@@ -4737,10 +5459,18 @@
       <c r="L93" s="2">
         <v>6</v>
       </c>
-      <c r="M93" s="5"/>
-      <c r="N93" s="5"/>
-      <c r="O93" s="5"/>
-      <c r="P93" s="5"/>
+      <c r="M93" s="2">
+        <v>28</v>
+      </c>
+      <c r="N93" s="2">
+        <v>6</v>
+      </c>
+      <c r="O93" s="2">
+        <v>29</v>
+      </c>
+      <c r="P93" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="94" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A94" s="3">
@@ -4779,10 +5509,18 @@
       <c r="L94" s="2">
         <v>8</v>
       </c>
-      <c r="M94" s="5"/>
-      <c r="N94" s="5"/>
-      <c r="O94" s="5"/>
-      <c r="P94" s="5"/>
+      <c r="M94" s="2">
+        <v>24</v>
+      </c>
+      <c r="N94" s="2">
+        <v>5</v>
+      </c>
+      <c r="O94" s="2">
+        <v>25</v>
+      </c>
+      <c r="P94" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="95" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A95" s="3">
@@ -4821,10 +5559,18 @@
       <c r="L95" s="2">
         <v>2</v>
       </c>
-      <c r="M95" s="5"/>
-      <c r="N95" s="5"/>
-      <c r="O95" s="5"/>
-      <c r="P95" s="5"/>
+      <c r="M95" s="2">
+        <v>20</v>
+      </c>
+      <c r="N95" s="2">
+        <v>3</v>
+      </c>
+      <c r="O95" s="2">
+        <v>21</v>
+      </c>
+      <c r="P95" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="96" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A96" s="3">
@@ -4863,10 +5609,18 @@
       <c r="L96" s="2">
         <v>6</v>
       </c>
-      <c r="M96" s="5"/>
-      <c r="N96" s="5"/>
-      <c r="O96" s="5"/>
-      <c r="P96" s="5"/>
+      <c r="M96" s="2">
+        <v>35</v>
+      </c>
+      <c r="N96" s="2">
+        <v>9</v>
+      </c>
+      <c r="O96" s="2">
+        <v>37</v>
+      </c>
+      <c r="P96" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="97" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A97" s="3">
@@ -4905,10 +5659,18 @@
       <c r="L97" s="2">
         <v>2</v>
       </c>
-      <c r="M97" s="5"/>
-      <c r="N97" s="5"/>
-      <c r="O97" s="5"/>
-      <c r="P97" s="5"/>
+      <c r="M97" s="2">
+        <v>24</v>
+      </c>
+      <c r="N97" s="2">
+        <v>5</v>
+      </c>
+      <c r="O97" s="2">
+        <v>25</v>
+      </c>
+      <c r="P97" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="98" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A98" s="3">
@@ -4947,10 +5709,18 @@
       <c r="L98" s="2">
         <v>6</v>
       </c>
-      <c r="M98" s="5"/>
-      <c r="N98" s="5"/>
-      <c r="O98" s="5"/>
-      <c r="P98" s="5"/>
+      <c r="M98" s="2">
+        <v>29</v>
+      </c>
+      <c r="N98" s="2">
+        <v>7</v>
+      </c>
+      <c r="O98" s="2">
+        <v>33</v>
+      </c>
+      <c r="P98" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="99" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A99" s="3">
@@ -4989,10 +5759,18 @@
       <c r="L99" s="2">
         <v>4</v>
       </c>
-      <c r="M99" s="5"/>
-      <c r="N99" s="5"/>
-      <c r="O99" s="5"/>
-      <c r="P99" s="5"/>
+      <c r="M99" s="2">
+        <v>27</v>
+      </c>
+      <c r="N99" s="2">
+        <v>5</v>
+      </c>
+      <c r="O99" s="2">
+        <v>28</v>
+      </c>
+      <c r="P99" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="100" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A100" s="3">
@@ -5031,10 +5809,18 @@
       <c r="L100" s="2">
         <v>4</v>
       </c>
-      <c r="M100" s="5"/>
-      <c r="N100" s="5"/>
-      <c r="O100" s="5"/>
-      <c r="P100" s="5"/>
+      <c r="M100" s="2">
+        <v>27</v>
+      </c>
+      <c r="N100" s="2">
+        <v>7</v>
+      </c>
+      <c r="O100" s="2">
+        <v>31</v>
+      </c>
+      <c r="P100" s="2">
+        <v>8</v>
+      </c>
     </row>
     <row r="101" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A101" s="3">
@@ -5073,10 +5859,18 @@
       <c r="L101" s="2">
         <v>4</v>
       </c>
-      <c r="M101" s="5"/>
-      <c r="N101" s="5"/>
-      <c r="O101" s="5"/>
-      <c r="P101" s="5"/>
+      <c r="M101" s="2">
+        <v>25</v>
+      </c>
+      <c r="N101" s="2">
+        <v>7</v>
+      </c>
+      <c r="O101" s="2">
+        <v>31</v>
+      </c>
+      <c r="P101" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="102" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A102" s="3">
@@ -5115,10 +5909,18 @@
       <c r="L102" s="2">
         <v>2</v>
       </c>
-      <c r="M102" s="5"/>
-      <c r="N102" s="5"/>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
+      <c r="M102" s="2">
+        <v>22</v>
+      </c>
+      <c r="N102" s="2">
+        <v>3</v>
+      </c>
+      <c r="O102" s="2">
+        <v>21</v>
+      </c>
+      <c r="P102" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="103" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A103" s="3">
@@ -5157,10 +5959,18 @@
       <c r="L103" s="2">
         <v>6</v>
       </c>
-      <c r="M103" s="5"/>
-      <c r="N103" s="5"/>
-      <c r="O103" s="5"/>
-      <c r="P103" s="5"/>
+      <c r="M103" s="2">
+        <v>25</v>
+      </c>
+      <c r="N103" s="2">
+        <v>5</v>
+      </c>
+      <c r="O103" s="2">
+        <v>27</v>
+      </c>
+      <c r="P103" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="104" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A104" s="3">
@@ -5199,10 +6009,18 @@
       <c r="L104" s="2">
         <v>1</v>
       </c>
-      <c r="M104" s="5"/>
-      <c r="N104" s="5"/>
-      <c r="O104" s="5"/>
-      <c r="P104" s="5"/>
+      <c r="M104" s="2">
+        <v>23</v>
+      </c>
+      <c r="N104" s="2">
+        <v>5</v>
+      </c>
+      <c r="O104" s="2">
+        <v>25</v>
+      </c>
+      <c r="P104" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="105" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A105" s="3">
@@ -5241,10 +6059,18 @@
       <c r="L105" s="2">
         <v>6</v>
       </c>
-      <c r="M105" s="5"/>
-      <c r="N105" s="5"/>
-      <c r="O105" s="5"/>
-      <c r="P105" s="5"/>
+      <c r="M105" s="2">
+        <v>25</v>
+      </c>
+      <c r="N105" s="2">
+        <v>5</v>
+      </c>
+      <c r="O105" s="2">
+        <v>27</v>
+      </c>
+      <c r="P105" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="106" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A106" s="3">
@@ -5283,10 +6109,18 @@
       <c r="L106" s="2">
         <v>6</v>
       </c>
-      <c r="M106" s="5"/>
-      <c r="N106" s="5"/>
-      <c r="O106" s="5"/>
-      <c r="P106" s="5"/>
+      <c r="M106" s="2">
+        <v>23</v>
+      </c>
+      <c r="N106" s="2">
+        <v>5</v>
+      </c>
+      <c r="O106" s="2">
+        <v>25</v>
+      </c>
+      <c r="P106" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="107" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A107" s="3">
@@ -5325,10 +6159,18 @@
       <c r="L107" s="2">
         <v>1</v>
       </c>
-      <c r="M107" s="5"/>
-      <c r="N107" s="5"/>
-      <c r="O107" s="5"/>
-      <c r="P107" s="5"/>
+      <c r="M107" s="2">
+        <v>18</v>
+      </c>
+      <c r="N107" s="2">
+        <v>2</v>
+      </c>
+      <c r="O107" s="2">
+        <v>16</v>
+      </c>
+      <c r="P107" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="108" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A108" s="3">
@@ -5367,10 +6209,18 @@
       <c r="L108" s="2">
         <v>4</v>
       </c>
-      <c r="M108" s="5"/>
-      <c r="N108" s="5"/>
-      <c r="O108" s="5"/>
-      <c r="P108" s="5"/>
+      <c r="M108" s="2">
+        <v>18</v>
+      </c>
+      <c r="N108" s="2">
+        <v>2</v>
+      </c>
+      <c r="O108" s="2">
+        <v>15</v>
+      </c>
+      <c r="P108" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="109" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A109" s="3">
@@ -5409,10 +6259,18 @@
       <c r="L109" s="2">
         <v>8</v>
       </c>
-      <c r="M109" s="5"/>
-      <c r="N109" s="5"/>
-      <c r="O109" s="5"/>
-      <c r="P109" s="5"/>
+      <c r="M109" s="2">
+        <v>20</v>
+      </c>
+      <c r="N109" s="2">
+        <v>4</v>
+      </c>
+      <c r="O109" s="2">
+        <v>22</v>
+      </c>
+      <c r="P109" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="110" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A110" s="3">
@@ -5451,10 +6309,18 @@
       <c r="L110" s="2">
         <v>10</v>
       </c>
-      <c r="M110" s="5"/>
-      <c r="N110" s="5"/>
-      <c r="O110" s="5"/>
-      <c r="P110" s="5"/>
+      <c r="M110" s="2">
+        <v>26</v>
+      </c>
+      <c r="N110" s="2">
+        <v>5</v>
+      </c>
+      <c r="O110" s="2">
+        <v>25</v>
+      </c>
+      <c r="P110" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="111" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A111" s="3">
@@ -5493,10 +6359,18 @@
       <c r="L111" s="2">
         <v>6</v>
       </c>
-      <c r="M111" s="5"/>
-      <c r="N111" s="5"/>
-      <c r="O111" s="5"/>
-      <c r="P111" s="5"/>
+      <c r="M111" s="2">
+        <v>24</v>
+      </c>
+      <c r="N111" s="2">
+        <v>5</v>
+      </c>
+      <c r="O111" s="2">
+        <v>25</v>
+      </c>
+      <c r="P111" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="112" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A112" s="3">
@@ -5518,7 +6392,7 @@
         <v>1</v>
       </c>
       <c r="G112" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H112" s="2">
         <v>0</v>
@@ -5532,11 +6406,21 @@
       <c r="K112" s="2">
         <v>0</v>
       </c>
-      <c r="L112" s="2"/>
-      <c r="M112" s="5"/>
-      <c r="N112" s="5"/>
-      <c r="O112" s="5"/>
-      <c r="P112" s="5"/>
+      <c r="L112" s="2">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2">
+        <v>0</v>
+      </c>
+      <c r="N112" s="2">
+        <v>0</v>
+      </c>
+      <c r="O112" s="2">
+        <v>0</v>
+      </c>
+      <c r="P112" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="113" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A113" s="3">
@@ -5575,10 +6459,18 @@
       <c r="L113" s="2">
         <v>2</v>
       </c>
-      <c r="M113" s="5"/>
-      <c r="N113" s="5"/>
-      <c r="O113" s="5"/>
-      <c r="P113" s="5"/>
+      <c r="M113" s="2">
+        <v>24</v>
+      </c>
+      <c r="N113" s="2">
+        <v>5</v>
+      </c>
+      <c r="O113" s="2">
+        <v>25</v>
+      </c>
+      <c r="P113" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="114" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A114" s="3">
@@ -5617,10 +6509,18 @@
       <c r="L114" s="2">
         <v>1</v>
       </c>
-      <c r="M114" s="5"/>
-      <c r="N114" s="5"/>
-      <c r="O114" s="5"/>
-      <c r="P114" s="5"/>
+      <c r="M114" s="2">
+        <v>25</v>
+      </c>
+      <c r="N114" s="2">
+        <v>5</v>
+      </c>
+      <c r="O114" s="2">
+        <v>25</v>
+      </c>
+      <c r="P114" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="115" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A115" s="3">
@@ -5659,10 +6559,18 @@
       <c r="L115" s="2">
         <v>1</v>
       </c>
-      <c r="M115" s="5"/>
-      <c r="N115" s="5"/>
-      <c r="O115" s="5"/>
-      <c r="P115" s="5"/>
+      <c r="M115" s="2">
+        <v>25</v>
+      </c>
+      <c r="N115" s="2">
+        <v>4</v>
+      </c>
+      <c r="O115" s="2">
+        <v>23</v>
+      </c>
+      <c r="P115" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="116" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A116" s="3">
@@ -5701,10 +6609,18 @@
       <c r="L116" s="2">
         <v>6</v>
       </c>
-      <c r="M116" s="5"/>
-      <c r="N116" s="5"/>
-      <c r="O116" s="5"/>
-      <c r="P116" s="5"/>
+      <c r="M116" s="2">
+        <v>24</v>
+      </c>
+      <c r="N116" s="2">
+        <v>4</v>
+      </c>
+      <c r="O116" s="2">
+        <v>23</v>
+      </c>
+      <c r="P116" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="117" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A117" s="3">
@@ -5743,10 +6659,18 @@
       <c r="L117" s="2">
         <v>1</v>
       </c>
-      <c r="M117" s="5"/>
-      <c r="N117" s="5"/>
-      <c r="O117" s="5"/>
-      <c r="P117" s="5"/>
+      <c r="M117" s="2">
+        <v>22</v>
+      </c>
+      <c r="N117" s="2">
+        <v>5</v>
+      </c>
+      <c r="O117" s="2">
+        <v>21</v>
+      </c>
+      <c r="P117" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="118" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A118" s="3">
@@ -5785,10 +6709,18 @@
       <c r="L118" s="2">
         <v>6</v>
       </c>
-      <c r="M118" s="5"/>
-      <c r="N118" s="5"/>
-      <c r="O118" s="5"/>
-      <c r="P118" s="5"/>
+      <c r="M118" s="2">
+        <v>21</v>
+      </c>
+      <c r="N118" s="2">
+        <v>5</v>
+      </c>
+      <c r="O118" s="2">
+        <v>21</v>
+      </c>
+      <c r="P118" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="119" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A119" s="3">
@@ -5827,10 +6759,18 @@
       <c r="L119" s="2">
         <v>4</v>
       </c>
-      <c r="M119" s="5"/>
-      <c r="N119" s="5"/>
-      <c r="O119" s="5"/>
-      <c r="P119" s="5"/>
+      <c r="M119" s="2">
+        <v>24</v>
+      </c>
+      <c r="N119" s="2">
+        <v>4</v>
+      </c>
+      <c r="O119" s="2">
+        <v>23</v>
+      </c>
+      <c r="P119" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="120" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A120" s="3">
@@ -5869,10 +6809,18 @@
       <c r="L120" s="2">
         <v>10</v>
       </c>
-      <c r="M120" s="5"/>
-      <c r="N120" s="5"/>
-      <c r="O120" s="5"/>
-      <c r="P120" s="5"/>
+      <c r="M120" s="2">
+        <v>32</v>
+      </c>
+      <c r="N120" s="2">
+        <v>8</v>
+      </c>
+      <c r="O120" s="2">
+        <v>34</v>
+      </c>
+      <c r="P120" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="121" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A121" s="3">
@@ -5911,10 +6859,18 @@
       <c r="L121" s="2">
         <v>6</v>
       </c>
-      <c r="M121" s="5"/>
-      <c r="N121" s="5"/>
-      <c r="O121" s="5"/>
-      <c r="P121" s="5"/>
+      <c r="M121" s="2">
+        <v>24</v>
+      </c>
+      <c r="N121" s="2">
+        <v>4</v>
+      </c>
+      <c r="O121" s="2">
+        <v>23</v>
+      </c>
+      <c r="P121" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="122" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A122" s="3">
@@ -5953,10 +6909,18 @@
       <c r="L122" s="2">
         <v>8</v>
       </c>
-      <c r="M122" s="5"/>
-      <c r="N122" s="5"/>
-      <c r="O122" s="5"/>
-      <c r="P122" s="5"/>
+      <c r="M122" s="2">
+        <v>26</v>
+      </c>
+      <c r="N122" s="2">
+        <v>6</v>
+      </c>
+      <c r="O122" s="2">
+        <v>27</v>
+      </c>
+      <c r="P122" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="123" spans="1:16" ht="21" x14ac:dyDescent="0.4">
       <c r="A123" s="3">
@@ -5995,778 +6959,518 @@
       <c r="L123" s="2">
         <v>10</v>
       </c>
-      <c r="M123" s="5"/>
-      <c r="N123" s="5"/>
-      <c r="O123" s="5"/>
-      <c r="P123" s="5"/>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A195" s="7"/>
-      <c r="B195" s="7"/>
-      <c r="C195" s="7"/>
-      <c r="D195" s="7"/>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A196" s="7"/>
-      <c r="B196" s="7"/>
-      <c r="C196" s="7"/>
-      <c r="D196" s="7"/>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A197" s="7"/>
-      <c r="B197" s="7"/>
-      <c r="C197" s="7"/>
-      <c r="D197" s="7"/>
-    </row>
-    <row r="198" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A198" s="8"/>
-      <c r="B198" s="8"/>
-      <c r="C198" s="7"/>
-      <c r="D198" s="7"/>
-    </row>
-    <row r="199" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A199" s="9"/>
-      <c r="B199" s="9"/>
-      <c r="C199" s="7"/>
-      <c r="D199" s="7"/>
-    </row>
-    <row r="200" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A200" s="9"/>
-      <c r="B200" s="9"/>
-      <c r="C200" s="7"/>
-      <c r="D200" s="7"/>
-    </row>
-    <row r="201" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A201" s="9"/>
-      <c r="B201" s="9"/>
-      <c r="C201" s="7"/>
-      <c r="D201" s="7"/>
-    </row>
-    <row r="202" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A202" s="9"/>
-      <c r="B202" s="9"/>
-      <c r="C202" s="7"/>
-      <c r="D202" s="7"/>
-    </row>
-    <row r="203" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A203" s="9"/>
-      <c r="B203" s="9"/>
-      <c r="C203" s="7"/>
-      <c r="D203" s="7"/>
-    </row>
-    <row r="204" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A204" s="9"/>
-      <c r="B204" s="9"/>
-      <c r="C204" s="7"/>
-      <c r="D204" s="7"/>
-    </row>
-    <row r="205" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A205" s="9"/>
-      <c r="B205" s="9"/>
-      <c r="C205" s="7"/>
-      <c r="D205" s="7"/>
-    </row>
-    <row r="206" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A206" s="9"/>
-      <c r="B206" s="9"/>
-      <c r="C206" s="7"/>
-      <c r="D206" s="7"/>
-    </row>
-    <row r="207" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A207" s="9"/>
-      <c r="B207" s="9"/>
-      <c r="C207" s="7"/>
-      <c r="D207" s="7"/>
-    </row>
-    <row r="208" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A208" s="9"/>
-      <c r="B208" s="9"/>
-      <c r="C208" s="7"/>
-      <c r="D208" s="7"/>
-    </row>
-    <row r="209" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A209" s="9"/>
-      <c r="B209" s="9"/>
-      <c r="C209" s="7"/>
-      <c r="D209" s="7"/>
-    </row>
-    <row r="210" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A210" s="9"/>
-      <c r="B210" s="9"/>
-      <c r="C210" s="7"/>
-      <c r="D210" s="7"/>
-    </row>
-    <row r="211" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A211" s="9"/>
-      <c r="B211" s="9"/>
-      <c r="C211" s="7"/>
-      <c r="D211" s="7"/>
-    </row>
-    <row r="212" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A212" s="9"/>
-      <c r="B212" s="9"/>
-      <c r="C212" s="7"/>
-      <c r="D212" s="7"/>
-    </row>
-    <row r="213" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A213" s="9"/>
-      <c r="B213" s="9"/>
-      <c r="C213" s="7"/>
-      <c r="D213" s="7"/>
-    </row>
-    <row r="214" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A214" s="9"/>
-      <c r="B214" s="9"/>
-      <c r="C214" s="7"/>
-      <c r="D214" s="7"/>
-    </row>
-    <row r="215" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A215" s="9"/>
-      <c r="B215" s="9"/>
-      <c r="C215" s="7"/>
-      <c r="D215" s="7"/>
-    </row>
-    <row r="216" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A216" s="9"/>
-      <c r="B216" s="9"/>
-      <c r="C216" s="7"/>
-      <c r="D216" s="7"/>
-    </row>
-    <row r="217" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A217" s="9"/>
-      <c r="B217" s="9"/>
-      <c r="C217" s="7"/>
-      <c r="D217" s="7"/>
-    </row>
-    <row r="218" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A218" s="9"/>
-      <c r="B218" s="9"/>
-      <c r="C218" s="7"/>
-      <c r="D218" s="7"/>
-    </row>
-    <row r="219" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A219" s="9"/>
-      <c r="B219" s="9"/>
-      <c r="C219" s="7"/>
-      <c r="D219" s="7"/>
-    </row>
-    <row r="220" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A220" s="9"/>
-      <c r="B220" s="9"/>
-      <c r="C220" s="7"/>
-      <c r="D220" s="7"/>
-    </row>
-    <row r="221" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A221" s="9"/>
-      <c r="B221" s="9"/>
-      <c r="C221" s="7"/>
-      <c r="D221" s="7"/>
-    </row>
-    <row r="222" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A222" s="9"/>
-      <c r="B222" s="9"/>
-      <c r="C222" s="7"/>
-      <c r="D222" s="7"/>
-    </row>
-    <row r="223" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A223" s="9"/>
-      <c r="B223" s="9"/>
-      <c r="C223" s="7"/>
-      <c r="D223" s="7"/>
-    </row>
-    <row r="224" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A224" s="9"/>
-      <c r="B224" s="9"/>
-      <c r="C224" s="7"/>
-      <c r="D224" s="7"/>
-    </row>
-    <row r="225" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A225" s="9"/>
-      <c r="B225" s="9"/>
-      <c r="C225" s="7"/>
-      <c r="D225" s="7"/>
-    </row>
-    <row r="226" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A226" s="9"/>
-      <c r="B226" s="9"/>
-      <c r="C226" s="7"/>
-      <c r="D226" s="7"/>
-    </row>
-    <row r="227" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A227" s="9"/>
-      <c r="B227" s="9"/>
-      <c r="C227" s="7"/>
-      <c r="D227" s="7"/>
-    </row>
-    <row r="228" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A228" s="9"/>
-      <c r="B228" s="9"/>
-      <c r="C228" s="7"/>
-      <c r="D228" s="7"/>
-    </row>
-    <row r="229" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A229" s="9"/>
-      <c r="B229" s="9"/>
-      <c r="C229" s="7"/>
-      <c r="D229" s="7"/>
-    </row>
-    <row r="230" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A230" s="9"/>
-      <c r="B230" s="9"/>
-      <c r="C230" s="7"/>
-      <c r="D230" s="7"/>
-    </row>
-    <row r="231" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A231" s="9"/>
-      <c r="B231" s="9"/>
-      <c r="C231" s="7"/>
-      <c r="D231" s="7"/>
-    </row>
-    <row r="232" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A232" s="9"/>
-      <c r="B232" s="9"/>
-      <c r="C232" s="7"/>
-      <c r="D232" s="7"/>
-    </row>
-    <row r="233" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A233" s="9"/>
-      <c r="B233" s="9"/>
-      <c r="C233" s="7"/>
-      <c r="D233" s="7"/>
-    </row>
-    <row r="234" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A234" s="9"/>
-      <c r="B234" s="9"/>
-      <c r="C234" s="7"/>
-      <c r="D234" s="7"/>
-    </row>
-    <row r="235" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A235" s="9"/>
-      <c r="B235" s="9"/>
-      <c r="C235" s="7"/>
-      <c r="D235" s="7"/>
-    </row>
-    <row r="236" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A236" s="9"/>
-      <c r="B236" s="9"/>
-      <c r="C236" s="7"/>
-      <c r="D236" s="7"/>
-    </row>
-    <row r="237" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A237" s="9"/>
-      <c r="B237" s="9"/>
-      <c r="C237" s="7"/>
-      <c r="D237" s="7"/>
-    </row>
-    <row r="238" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A238" s="9"/>
-      <c r="B238" s="9"/>
-      <c r="C238" s="7"/>
-      <c r="D238" s="7"/>
-    </row>
-    <row r="239" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A239" s="9"/>
-      <c r="B239" s="9"/>
-      <c r="C239" s="7"/>
-      <c r="D239" s="7"/>
-    </row>
-    <row r="240" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A240" s="9"/>
-      <c r="B240" s="9"/>
-      <c r="C240" s="7"/>
-      <c r="D240" s="7"/>
-    </row>
-    <row r="241" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A241" s="9"/>
-      <c r="B241" s="9"/>
-      <c r="C241" s="7"/>
-      <c r="D241" s="7"/>
-    </row>
-    <row r="242" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A242" s="9"/>
-      <c r="B242" s="9"/>
-      <c r="C242" s="7"/>
-      <c r="D242" s="7"/>
-    </row>
-    <row r="243" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A243" s="9"/>
-      <c r="B243" s="9"/>
-      <c r="C243" s="7"/>
-      <c r="D243" s="7"/>
-    </row>
-    <row r="244" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A244" s="9"/>
-      <c r="B244" s="9"/>
-      <c r="C244" s="7"/>
-      <c r="D244" s="7"/>
-    </row>
-    <row r="245" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A245" s="9"/>
-      <c r="B245" s="9"/>
-      <c r="C245" s="7"/>
-      <c r="D245" s="7"/>
-    </row>
-    <row r="246" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A246" s="9"/>
-      <c r="B246" s="9"/>
-      <c r="C246" s="7"/>
-      <c r="D246" s="7"/>
-    </row>
-    <row r="247" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A247" s="9"/>
-      <c r="B247" s="9"/>
-      <c r="C247" s="7"/>
-      <c r="D247" s="7"/>
-    </row>
-    <row r="248" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A248" s="9"/>
-      <c r="B248" s="9"/>
-      <c r="C248" s="7"/>
-      <c r="D248" s="7"/>
-    </row>
-    <row r="249" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A249" s="9"/>
-      <c r="B249" s="9"/>
-      <c r="C249" s="7"/>
-      <c r="D249" s="7"/>
-    </row>
-    <row r="250" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A250" s="9"/>
-      <c r="B250" s="9"/>
-      <c r="C250" s="7"/>
-      <c r="D250" s="7"/>
-    </row>
-    <row r="251" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A251" s="9"/>
-      <c r="B251" s="9"/>
-      <c r="C251" s="7"/>
-      <c r="D251" s="7"/>
-    </row>
-    <row r="252" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A252" s="9"/>
-      <c r="B252" s="9"/>
-      <c r="C252" s="7"/>
-      <c r="D252" s="7"/>
-    </row>
-    <row r="253" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A253" s="9"/>
-      <c r="B253" s="9"/>
-      <c r="C253" s="7"/>
-      <c r="D253" s="7"/>
-    </row>
-    <row r="254" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A254" s="9"/>
-      <c r="B254" s="9"/>
-      <c r="C254" s="7"/>
-      <c r="D254" s="7"/>
-    </row>
-    <row r="255" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A255" s="9"/>
-      <c r="B255" s="9"/>
-      <c r="C255" s="7"/>
-      <c r="D255" s="7"/>
-    </row>
-    <row r="256" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A256" s="9"/>
-      <c r="B256" s="9"/>
-      <c r="C256" s="7"/>
-      <c r="D256" s="7"/>
-    </row>
-    <row r="257" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A257" s="9"/>
-      <c r="B257" s="9"/>
-      <c r="C257" s="7"/>
-      <c r="D257" s="7"/>
-    </row>
-    <row r="258" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A258" s="9"/>
-      <c r="B258" s="9"/>
-      <c r="C258" s="7"/>
-      <c r="D258" s="7"/>
-    </row>
-    <row r="259" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A259" s="9"/>
-      <c r="B259" s="9"/>
-      <c r="C259" s="7"/>
-      <c r="D259" s="7"/>
-    </row>
-    <row r="260" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A260" s="9"/>
-      <c r="B260" s="9"/>
-      <c r="C260" s="7"/>
-      <c r="D260" s="7"/>
-    </row>
-    <row r="261" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A261" s="9"/>
-      <c r="B261" s="9"/>
-      <c r="C261" s="7"/>
-      <c r="D261" s="7"/>
-    </row>
-    <row r="262" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A262" s="9"/>
-      <c r="B262" s="9"/>
-      <c r="C262" s="7"/>
-      <c r="D262" s="7"/>
-    </row>
-    <row r="263" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A263" s="9"/>
-      <c r="B263" s="9"/>
-      <c r="C263" s="7"/>
-      <c r="D263" s="7"/>
-    </row>
-    <row r="264" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A264" s="9"/>
-      <c r="B264" s="9"/>
-      <c r="C264" s="7"/>
-      <c r="D264" s="7"/>
-    </row>
-    <row r="265" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A265" s="9"/>
-      <c r="B265" s="9"/>
-      <c r="C265" s="7"/>
-      <c r="D265" s="7"/>
-    </row>
-    <row r="266" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A266" s="9"/>
-      <c r="B266" s="9"/>
-      <c r="C266" s="7"/>
-      <c r="D266" s="7"/>
-    </row>
-    <row r="267" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A267" s="9"/>
-      <c r="B267" s="9"/>
-      <c r="C267" s="7"/>
-      <c r="D267" s="7"/>
-    </row>
-    <row r="268" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A268" s="9"/>
-      <c r="B268" s="9"/>
-      <c r="C268" s="7"/>
-      <c r="D268" s="7"/>
-    </row>
-    <row r="269" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A269" s="9"/>
-      <c r="B269" s="9"/>
-      <c r="C269" s="7"/>
-      <c r="D269" s="7"/>
-    </row>
-    <row r="270" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A270" s="9"/>
-      <c r="B270" s="9"/>
-      <c r="C270" s="7"/>
-      <c r="D270" s="7"/>
-    </row>
-    <row r="271" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A271" s="9"/>
-      <c r="B271" s="9"/>
-      <c r="C271" s="7"/>
-      <c r="D271" s="7"/>
-    </row>
-    <row r="272" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A272" s="9"/>
-      <c r="B272" s="9"/>
-      <c r="C272" s="7"/>
-      <c r="D272" s="7"/>
-    </row>
-    <row r="273" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A273" s="9"/>
-      <c r="B273" s="9"/>
-      <c r="C273" s="7"/>
-      <c r="D273" s="7"/>
-    </row>
-    <row r="274" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A274" s="9"/>
-      <c r="B274" s="9"/>
-      <c r="C274" s="7"/>
-      <c r="D274" s="7"/>
-    </row>
-    <row r="275" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A275" s="9"/>
-      <c r="B275" s="9"/>
-      <c r="C275" s="7"/>
-      <c r="D275" s="7"/>
-    </row>
-    <row r="276" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A276" s="9"/>
-      <c r="B276" s="9"/>
-      <c r="C276" s="7"/>
-      <c r="D276" s="7"/>
-    </row>
-    <row r="277" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A277" s="9"/>
-      <c r="B277" s="9"/>
-      <c r="C277" s="7"/>
-      <c r="D277" s="7"/>
-    </row>
-    <row r="278" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A278" s="9"/>
-      <c r="B278" s="9"/>
-      <c r="C278" s="7"/>
-      <c r="D278" s="7"/>
-    </row>
-    <row r="279" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A279" s="9"/>
-      <c r="B279" s="9"/>
-      <c r="C279" s="7"/>
-      <c r="D279" s="7"/>
-    </row>
-    <row r="280" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A280" s="9"/>
-      <c r="B280" s="9"/>
-      <c r="C280" s="7"/>
-      <c r="D280" s="7"/>
-    </row>
-    <row r="281" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A281" s="9"/>
-      <c r="B281" s="9"/>
-      <c r="C281" s="7"/>
-      <c r="D281" s="7"/>
-    </row>
-    <row r="282" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A282" s="9"/>
-      <c r="B282" s="9"/>
-      <c r="C282" s="7"/>
-      <c r="D282" s="7"/>
-    </row>
-    <row r="283" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A283" s="9"/>
-      <c r="B283" s="9"/>
-      <c r="C283" s="7"/>
-      <c r="D283" s="7"/>
-    </row>
-    <row r="284" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A284" s="9"/>
-      <c r="B284" s="9"/>
-      <c r="C284" s="7"/>
-      <c r="D284" s="7"/>
-    </row>
-    <row r="285" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A285" s="9"/>
-      <c r="B285" s="9"/>
-      <c r="C285" s="7"/>
-      <c r="D285" s="7"/>
-    </row>
-    <row r="286" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A286" s="9"/>
-      <c r="B286" s="9"/>
-      <c r="C286" s="7"/>
-      <c r="D286" s="7"/>
-    </row>
-    <row r="287" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A287" s="9"/>
-      <c r="B287" s="9"/>
-      <c r="C287" s="7"/>
-      <c r="D287" s="7"/>
-    </row>
-    <row r="288" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A288" s="9"/>
-      <c r="B288" s="9"/>
-      <c r="C288" s="7"/>
-      <c r="D288" s="7"/>
-    </row>
-    <row r="289" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A289" s="9"/>
-      <c r="B289" s="9"/>
-      <c r="C289" s="7"/>
-      <c r="D289" s="7"/>
-    </row>
-    <row r="290" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A290" s="9"/>
-      <c r="B290" s="9"/>
-      <c r="C290" s="7"/>
-      <c r="D290" s="7"/>
-    </row>
-    <row r="291" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A291" s="9"/>
-      <c r="B291" s="9"/>
-      <c r="C291" s="7"/>
-      <c r="D291" s="7"/>
-    </row>
-    <row r="292" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A292" s="9"/>
-      <c r="B292" s="9"/>
-      <c r="C292" s="7"/>
-      <c r="D292" s="7"/>
-    </row>
-    <row r="293" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A293" s="9"/>
-      <c r="B293" s="9"/>
-      <c r="C293" s="7"/>
-      <c r="D293" s="7"/>
-    </row>
-    <row r="294" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A294" s="9"/>
-      <c r="B294" s="9"/>
-      <c r="C294" s="7"/>
-      <c r="D294" s="7"/>
-    </row>
-    <row r="295" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A295" s="9"/>
-      <c r="B295" s="9"/>
-      <c r="C295" s="7"/>
-      <c r="D295" s="7"/>
-    </row>
-    <row r="296" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A296" s="9"/>
-      <c r="B296" s="9"/>
-      <c r="C296" s="7"/>
-      <c r="D296" s="7"/>
-    </row>
-    <row r="297" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A297" s="9"/>
-      <c r="B297" s="9"/>
-      <c r="C297" s="7"/>
-      <c r="D297" s="7"/>
-    </row>
-    <row r="298" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A298" s="9"/>
-      <c r="B298" s="9"/>
-      <c r="C298" s="7"/>
-      <c r="D298" s="7"/>
-    </row>
-    <row r="299" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A299" s="9"/>
-      <c r="B299" s="9"/>
-      <c r="C299" s="7"/>
-      <c r="D299" s="7"/>
-    </row>
-    <row r="300" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A300" s="9"/>
-      <c r="B300" s="9"/>
-      <c r="C300" s="7"/>
-      <c r="D300" s="7"/>
-    </row>
-    <row r="301" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A301" s="9"/>
-      <c r="B301" s="9"/>
-      <c r="C301" s="7"/>
-      <c r="D301" s="7"/>
-    </row>
-    <row r="302" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A302" s="9"/>
-      <c r="B302" s="9"/>
-      <c r="C302" s="7"/>
-      <c r="D302" s="7"/>
-    </row>
-    <row r="303" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A303" s="9"/>
-      <c r="B303" s="9"/>
-      <c r="C303" s="7"/>
-      <c r="D303" s="7"/>
-    </row>
-    <row r="304" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A304" s="9"/>
-      <c r="B304" s="9"/>
-      <c r="C304" s="7"/>
-      <c r="D304" s="7"/>
-    </row>
-    <row r="305" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A305" s="9"/>
-      <c r="B305" s="9"/>
-      <c r="C305" s="7"/>
-      <c r="D305" s="7"/>
-    </row>
-    <row r="306" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A306" s="9"/>
-      <c r="B306" s="9"/>
-      <c r="C306" s="7"/>
-      <c r="D306" s="7"/>
-    </row>
-    <row r="307" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A307" s="9"/>
-      <c r="B307" s="9"/>
-      <c r="C307" s="7"/>
-      <c r="D307" s="7"/>
-    </row>
-    <row r="308" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A308" s="9"/>
-      <c r="B308" s="9"/>
-      <c r="C308" s="7"/>
-      <c r="D308" s="7"/>
-    </row>
-    <row r="309" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A309" s="9"/>
-      <c r="B309" s="9"/>
-      <c r="C309" s="7"/>
-      <c r="D309" s="7"/>
-    </row>
-    <row r="310" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A310" s="9"/>
-      <c r="B310" s="9"/>
-      <c r="C310" s="7"/>
-      <c r="D310" s="7"/>
-    </row>
-    <row r="311" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A311" s="9"/>
-      <c r="B311" s="9"/>
-      <c r="C311" s="7"/>
-      <c r="D311" s="7"/>
-    </row>
-    <row r="312" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A312" s="9"/>
-      <c r="B312" s="9"/>
-      <c r="C312" s="7"/>
-      <c r="D312" s="7"/>
-    </row>
-    <row r="313" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A313" s="9"/>
-      <c r="B313" s="9"/>
-      <c r="C313" s="7"/>
-      <c r="D313" s="7"/>
-    </row>
-    <row r="314" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A314" s="9"/>
-      <c r="B314" s="9"/>
-      <c r="C314" s="7"/>
-      <c r="D314" s="7"/>
-    </row>
-    <row r="315" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A315" s="9"/>
-      <c r="B315" s="9"/>
-      <c r="C315" s="7"/>
-      <c r="D315" s="7"/>
-    </row>
-    <row r="316" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A316" s="9"/>
-      <c r="B316" s="9"/>
-      <c r="C316" s="7"/>
-      <c r="D316" s="7"/>
-    </row>
-    <row r="317" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A317" s="9"/>
-      <c r="B317" s="9"/>
-      <c r="C317" s="7"/>
-      <c r="D317" s="7"/>
-    </row>
-    <row r="318" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A318" s="9"/>
-      <c r="B318" s="9"/>
-      <c r="C318" s="7"/>
-      <c r="D318" s="7"/>
-    </row>
-    <row r="319" spans="1:4" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A319" s="9"/>
-      <c r="B319" s="9"/>
-      <c r="C319" s="7"/>
-      <c r="D319" s="7"/>
-    </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A320" s="7"/>
-      <c r="B320" s="7"/>
-      <c r="C320" s="7"/>
-      <c r="D320" s="7"/>
+      <c r="M123" s="2">
+        <v>34</v>
+      </c>
+      <c r="N123" s="2">
+        <v>10</v>
+      </c>
+      <c r="O123" s="2">
+        <v>38</v>
+      </c>
+      <c r="P123" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A198" s="4"/>
+      <c r="B198" s="4"/>
+    </row>
+    <row r="199" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A199" s="5"/>
+      <c r="B199" s="5"/>
+    </row>
+    <row r="200" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A200" s="5"/>
+      <c r="B200" s="5"/>
+    </row>
+    <row r="201" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A201" s="5"/>
+      <c r="B201" s="5"/>
+    </row>
+    <row r="202" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A202" s="5"/>
+      <c r="B202" s="5"/>
+    </row>
+    <row r="203" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A203" s="5"/>
+      <c r="B203" s="5"/>
+    </row>
+    <row r="204" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A204" s="5"/>
+      <c r="B204" s="5"/>
+    </row>
+    <row r="205" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A205" s="5"/>
+      <c r="B205" s="5"/>
+    </row>
+    <row r="206" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A206" s="5"/>
+      <c r="B206" s="5"/>
+    </row>
+    <row r="207" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A207" s="5"/>
+      <c r="B207" s="5"/>
+    </row>
+    <row r="208" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A208" s="5"/>
+      <c r="B208" s="5"/>
+    </row>
+    <row r="209" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A209" s="5"/>
+      <c r="B209" s="5"/>
+    </row>
+    <row r="210" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A210" s="5"/>
+      <c r="B210" s="5"/>
+    </row>
+    <row r="211" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A211" s="5"/>
+      <c r="B211" s="5"/>
+    </row>
+    <row r="212" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A212" s="5"/>
+      <c r="B212" s="5"/>
+    </row>
+    <row r="213" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A213" s="5"/>
+      <c r="B213" s="5"/>
+    </row>
+    <row r="214" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A214" s="5"/>
+      <c r="B214" s="5"/>
+    </row>
+    <row r="215" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A215" s="5"/>
+      <c r="B215" s="5"/>
+    </row>
+    <row r="216" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A216" s="5"/>
+      <c r="B216" s="5"/>
+    </row>
+    <row r="217" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A217" s="5"/>
+      <c r="B217" s="5"/>
+    </row>
+    <row r="218" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A218" s="5"/>
+      <c r="B218" s="5"/>
+    </row>
+    <row r="219" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A219" s="5"/>
+      <c r="B219" s="5"/>
+    </row>
+    <row r="220" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A220" s="5"/>
+      <c r="B220" s="5"/>
+    </row>
+    <row r="221" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A221" s="5"/>
+      <c r="B221" s="5"/>
+    </row>
+    <row r="222" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A222" s="5"/>
+      <c r="B222" s="5"/>
+    </row>
+    <row r="223" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A223" s="5"/>
+      <c r="B223" s="5"/>
+    </row>
+    <row r="224" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A224" s="5"/>
+      <c r="B224" s="5"/>
+    </row>
+    <row r="225" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A225" s="5"/>
+      <c r="B225" s="5"/>
+    </row>
+    <row r="226" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A226" s="5"/>
+      <c r="B226" s="5"/>
+    </row>
+    <row r="227" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A227" s="5"/>
+      <c r="B227" s="5"/>
+    </row>
+    <row r="228" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A228" s="5"/>
+      <c r="B228" s="5"/>
+    </row>
+    <row r="229" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A229" s="5"/>
+      <c r="B229" s="5"/>
+    </row>
+    <row r="230" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A230" s="5"/>
+      <c r="B230" s="5"/>
+    </row>
+    <row r="231" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A231" s="5"/>
+      <c r="B231" s="5"/>
+    </row>
+    <row r="232" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A232" s="5"/>
+      <c r="B232" s="5"/>
+    </row>
+    <row r="233" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A233" s="5"/>
+      <c r="B233" s="5"/>
+    </row>
+    <row r="234" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A234" s="5"/>
+      <c r="B234" s="5"/>
+    </row>
+    <row r="235" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A235" s="5"/>
+      <c r="B235" s="5"/>
+    </row>
+    <row r="236" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A236" s="5"/>
+      <c r="B236" s="5"/>
+    </row>
+    <row r="237" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A237" s="5"/>
+      <c r="B237" s="5"/>
+    </row>
+    <row r="238" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A238" s="5"/>
+      <c r="B238" s="5"/>
+    </row>
+    <row r="239" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A239" s="5"/>
+      <c r="B239" s="5"/>
+    </row>
+    <row r="240" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A240" s="5"/>
+      <c r="B240" s="5"/>
+    </row>
+    <row r="241" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A241" s="5"/>
+      <c r="B241" s="5"/>
+    </row>
+    <row r="242" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A242" s="5"/>
+      <c r="B242" s="5"/>
+    </row>
+    <row r="243" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A243" s="5"/>
+      <c r="B243" s="5"/>
+    </row>
+    <row r="244" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A244" s="5"/>
+      <c r="B244" s="5"/>
+    </row>
+    <row r="245" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A245" s="5"/>
+      <c r="B245" s="5"/>
+    </row>
+    <row r="246" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A246" s="5"/>
+      <c r="B246" s="5"/>
+    </row>
+    <row r="247" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A247" s="5"/>
+      <c r="B247" s="5"/>
+    </row>
+    <row r="248" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A248" s="5"/>
+      <c r="B248" s="5"/>
+    </row>
+    <row r="249" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A249" s="5"/>
+      <c r="B249" s="5"/>
+    </row>
+    <row r="250" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A250" s="5"/>
+      <c r="B250" s="5"/>
+    </row>
+    <row r="251" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A251" s="5"/>
+      <c r="B251" s="5"/>
+    </row>
+    <row r="252" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A252" s="5"/>
+      <c r="B252" s="5"/>
+    </row>
+    <row r="253" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A253" s="5"/>
+      <c r="B253" s="5"/>
+    </row>
+    <row r="254" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A254" s="5"/>
+      <c r="B254" s="5"/>
+    </row>
+    <row r="255" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A255" s="5"/>
+      <c r="B255" s="5"/>
+    </row>
+    <row r="256" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A256" s="5"/>
+      <c r="B256" s="5"/>
+    </row>
+    <row r="257" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A257" s="5"/>
+      <c r="B257" s="5"/>
+    </row>
+    <row r="258" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A258" s="5"/>
+      <c r="B258" s="5"/>
+    </row>
+    <row r="259" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A259" s="5"/>
+      <c r="B259" s="5"/>
+    </row>
+    <row r="260" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A260" s="5"/>
+      <c r="B260" s="5"/>
+    </row>
+    <row r="261" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A261" s="5"/>
+      <c r="B261" s="5"/>
+    </row>
+    <row r="262" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A262" s="5"/>
+      <c r="B262" s="5"/>
+    </row>
+    <row r="263" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A263" s="5"/>
+      <c r="B263" s="5"/>
+    </row>
+    <row r="264" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A264" s="5"/>
+      <c r="B264" s="5"/>
+    </row>
+    <row r="265" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A265" s="5"/>
+      <c r="B265" s="5"/>
+    </row>
+    <row r="266" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A266" s="5"/>
+      <c r="B266" s="5"/>
+    </row>
+    <row r="267" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A267" s="5"/>
+      <c r="B267" s="5"/>
+    </row>
+    <row r="268" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A268" s="5"/>
+      <c r="B268" s="5"/>
+    </row>
+    <row r="269" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A269" s="5"/>
+      <c r="B269" s="5"/>
+    </row>
+    <row r="270" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A270" s="5"/>
+      <c r="B270" s="5"/>
+    </row>
+    <row r="271" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A271" s="5"/>
+      <c r="B271" s="5"/>
+    </row>
+    <row r="272" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A272" s="5"/>
+      <c r="B272" s="5"/>
+    </row>
+    <row r="273" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A273" s="5"/>
+      <c r="B273" s="5"/>
+    </row>
+    <row r="274" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A274" s="5"/>
+      <c r="B274" s="5"/>
+    </row>
+    <row r="275" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A275" s="5"/>
+      <c r="B275" s="5"/>
+    </row>
+    <row r="276" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A276" s="5"/>
+      <c r="B276" s="5"/>
+    </row>
+    <row r="277" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A277" s="5"/>
+      <c r="B277" s="5"/>
+    </row>
+    <row r="278" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A278" s="5"/>
+      <c r="B278" s="5"/>
+    </row>
+    <row r="279" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A279" s="5"/>
+      <c r="B279" s="5"/>
+    </row>
+    <row r="280" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A280" s="5"/>
+      <c r="B280" s="5"/>
+    </row>
+    <row r="281" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A281" s="5"/>
+      <c r="B281" s="5"/>
+    </row>
+    <row r="282" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A282" s="5"/>
+      <c r="B282" s="5"/>
+    </row>
+    <row r="283" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A283" s="5"/>
+      <c r="B283" s="5"/>
+    </row>
+    <row r="284" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A284" s="5"/>
+      <c r="B284" s="5"/>
+    </row>
+    <row r="285" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A285" s="5"/>
+      <c r="B285" s="5"/>
+    </row>
+    <row r="286" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A286" s="5"/>
+      <c r="B286" s="5"/>
+    </row>
+    <row r="287" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A287" s="5"/>
+      <c r="B287" s="5"/>
+    </row>
+    <row r="288" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A288" s="5"/>
+      <c r="B288" s="5"/>
+    </row>
+    <row r="289" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A289" s="5"/>
+      <c r="B289" s="5"/>
+    </row>
+    <row r="290" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A290" s="5"/>
+      <c r="B290" s="5"/>
+    </row>
+    <row r="291" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A291" s="5"/>
+      <c r="B291" s="5"/>
+    </row>
+    <row r="292" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A292" s="5"/>
+      <c r="B292" s="5"/>
+    </row>
+    <row r="293" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A293" s="5"/>
+      <c r="B293" s="5"/>
+    </row>
+    <row r="294" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A294" s="5"/>
+      <c r="B294" s="5"/>
+    </row>
+    <row r="295" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A295" s="5"/>
+      <c r="B295" s="5"/>
+    </row>
+    <row r="296" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A296" s="5"/>
+      <c r="B296" s="5"/>
+    </row>
+    <row r="297" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A297" s="5"/>
+      <c r="B297" s="5"/>
+    </row>
+    <row r="298" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A298" s="5"/>
+      <c r="B298" s="5"/>
+    </row>
+    <row r="299" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A299" s="5"/>
+      <c r="B299" s="5"/>
+    </row>
+    <row r="300" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A300" s="5"/>
+      <c r="B300" s="5"/>
+    </row>
+    <row r="301" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A301" s="5"/>
+      <c r="B301" s="5"/>
+    </row>
+    <row r="302" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A302" s="5"/>
+      <c r="B302" s="5"/>
+    </row>
+    <row r="303" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A303" s="5"/>
+      <c r="B303" s="5"/>
+    </row>
+    <row r="304" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A304" s="5"/>
+      <c r="B304" s="5"/>
+    </row>
+    <row r="305" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A305" s="5"/>
+      <c r="B305" s="5"/>
+    </row>
+    <row r="306" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A306" s="5"/>
+      <c r="B306" s="5"/>
+    </row>
+    <row r="307" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A307" s="5"/>
+      <c r="B307" s="5"/>
+    </row>
+    <row r="308" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A308" s="5"/>
+      <c r="B308" s="5"/>
+    </row>
+    <row r="309" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A309" s="5"/>
+      <c r="B309" s="5"/>
+    </row>
+    <row r="310" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A310" s="5"/>
+      <c r="B310" s="5"/>
+    </row>
+    <row r="311" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A311" s="5"/>
+      <c r="B311" s="5"/>
+    </row>
+    <row r="312" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A312" s="5"/>
+      <c r="B312" s="5"/>
+    </row>
+    <row r="313" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A313" s="5"/>
+      <c r="B313" s="5"/>
+    </row>
+    <row r="314" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A314" s="5"/>
+      <c r="B314" s="5"/>
+    </row>
+    <row r="315" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A315" s="5"/>
+      <c r="B315" s="5"/>
+    </row>
+    <row r="316" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A316" s="5"/>
+      <c r="B316" s="5"/>
+    </row>
+    <row r="317" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A317" s="5"/>
+      <c r="B317" s="5"/>
+    </row>
+    <row r="318" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A318" s="5"/>
+      <c r="B318" s="5"/>
+    </row>
+    <row r="319" spans="1:2" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A319" s="5"/>
+      <c r="B319" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="B1:B2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="M1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="B1:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/m2.xlsx
+++ b/m2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\سعيات\م2 - ف2\steam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADAEAF2-928D-4DF1-ACB3-0C692772A8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0331E7-6BE0-4417-96E1-37ACD24452AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -475,7 +475,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -485,6 +485,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -516,7 +522,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -533,10 +539,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -841,44 +853,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7" t="s">
+      <c r="D1" s="6"/>
+      <c r="E1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7" t="s">
+      <c r="F1" s="6"/>
+      <c r="G1" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7" t="s">
+      <c r="H1" s="6"/>
+      <c r="I1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7" t="s">
+      <c r="J1" s="6"/>
+      <c r="K1" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7" t="s">
+      <c r="L1" s="6"/>
+      <c r="M1" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7" t="s">
+      <c r="N1" s="6"/>
+      <c r="O1" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="P1" s="7"/>
+      <c r="P1" s="6"/>
     </row>
     <row r="2" spans="1:16" ht="21" x14ac:dyDescent="0.3">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3082,8 +3094,8 @@
       <c r="C46" s="2">
         <v>35</v>
       </c>
-      <c r="D46" s="2">
-        <v>8</v>
+      <c r="D46" s="8">
+        <v>10</v>
       </c>
       <c r="E46" s="2">
         <v>32</v>
@@ -3129,14 +3141,14 @@
       <c r="B47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C47" s="2">
-        <v>21</v>
+      <c r="C47" s="8">
+        <v>25</v>
       </c>
       <c r="D47" s="2">
         <v>5</v>
       </c>
-      <c r="E47" s="2">
-        <v>20</v>
+      <c r="E47" s="8">
+        <v>23</v>
       </c>
       <c r="F47" s="2">
         <v>5</v>
@@ -3185,11 +3197,11 @@
       <c r="D48" s="2">
         <v>10</v>
       </c>
-      <c r="E48" s="2">
-        <v>33</v>
-      </c>
-      <c r="F48" s="2">
-        <v>7</v>
+      <c r="E48" s="8">
+        <v>34</v>
+      </c>
+      <c r="F48" s="8">
+        <v>10</v>
       </c>
       <c r="G48" s="2">
         <v>37</v>
@@ -4079,8 +4091,8 @@
       <c r="B66" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C66" s="2">
-        <v>36</v>
+      <c r="C66" s="8">
+        <v>39</v>
       </c>
       <c r="D66" s="2">
         <v>10</v>
@@ -4803,8 +4815,8 @@
       <c r="J80" s="2">
         <v>8</v>
       </c>
-      <c r="K80" s="2">
-        <v>16</v>
+      <c r="K80" s="9">
+        <v>21</v>
       </c>
       <c r="L80" s="2">
         <v>2</v>
@@ -4979,20 +4991,20 @@
       <c r="B84" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C84" s="2">
-        <v>38</v>
+      <c r="C84" s="8">
+        <v>39</v>
       </c>
       <c r="D84" s="2">
         <v>10</v>
       </c>
-      <c r="E84" s="2">
-        <v>31</v>
+      <c r="E84" s="8">
+        <v>34</v>
       </c>
       <c r="F84" s="2">
         <v>10</v>
       </c>
-      <c r="G84" s="2">
-        <v>33</v>
+      <c r="G84" s="8">
+        <v>35</v>
       </c>
       <c r="H84" s="2">
         <v>10</v>
@@ -5685,8 +5697,8 @@
       <c r="D98" s="2">
         <v>8</v>
       </c>
-      <c r="E98" s="2">
-        <v>20</v>
+      <c r="E98" s="8">
+        <v>25</v>
       </c>
       <c r="F98" s="2">
         <v>10</v>
@@ -6335,8 +6347,8 @@
       <c r="D111" s="2">
         <v>5</v>
       </c>
-      <c r="E111" s="2">
-        <v>20</v>
+      <c r="E111" s="8">
+        <v>22</v>
       </c>
       <c r="F111" s="2">
         <v>1</v>
@@ -6354,7 +6366,7 @@
         <v>8</v>
       </c>
       <c r="K111" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L111" s="2">
         <v>6</v>
@@ -6788,11 +6800,11 @@
       <c r="E120" s="2">
         <v>29</v>
       </c>
-      <c r="F120" s="2">
-        <v>2</v>
-      </c>
-      <c r="G120" s="2">
-        <v>28</v>
+      <c r="F120" s="8">
+        <v>7</v>
+      </c>
+      <c r="G120" s="8">
+        <v>31</v>
       </c>
       <c r="H120" s="2">
         <v>7</v>
@@ -6935,17 +6947,17 @@
       <c r="D123" s="2">
         <v>9</v>
       </c>
-      <c r="E123" s="2">
-        <v>26</v>
+      <c r="E123" s="8">
+        <v>30</v>
       </c>
       <c r="F123" s="2">
         <v>8</v>
       </c>
-      <c r="G123" s="2">
-        <v>27</v>
-      </c>
-      <c r="H123" s="2">
-        <v>7</v>
+      <c r="G123" s="8">
+        <v>29</v>
+      </c>
+      <c r="H123" s="8">
+        <v>10</v>
       </c>
       <c r="I123" s="2">
         <v>34</v>

--- a/m2.xlsx
+++ b/m2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\سعيات\م2 - ف2\steam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0331E7-6BE0-4417-96E1-37ACD24452AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DBC2876-F79E-49FF-8F04-8A41FBE2E52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -522,7 +522,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -539,17 +539,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -853,44 +850,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="7"/>
+      <c r="E1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6" t="s">
+      <c r="F1" s="7"/>
+      <c r="G1" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6" t="s">
+      <c r="H1" s="7"/>
+      <c r="I1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6" t="s">
+      <c r="J1" s="7"/>
+      <c r="K1" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6" t="s">
+      <c r="L1" s="7"/>
+      <c r="M1" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6" t="s">
+      <c r="N1" s="7"/>
+      <c r="O1" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="P1" s="6"/>
+      <c r="P1" s="7"/>
     </row>
     <row r="2" spans="1:16" ht="21" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3094,7 +3091,7 @@
       <c r="C46" s="2">
         <v>35</v>
       </c>
-      <c r="D46" s="8">
+      <c r="D46" s="6">
         <v>10</v>
       </c>
       <c r="E46" s="2">
@@ -3141,13 +3138,13 @@
       <c r="B47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C47" s="8">
+      <c r="C47" s="6">
         <v>25</v>
       </c>
       <c r="D47" s="2">
         <v>5</v>
       </c>
-      <c r="E47" s="8">
+      <c r="E47" s="6">
         <v>23</v>
       </c>
       <c r="F47" s="2">
@@ -3197,10 +3194,10 @@
       <c r="D48" s="2">
         <v>10</v>
       </c>
-      <c r="E48" s="8">
+      <c r="E48" s="6">
         <v>34</v>
       </c>
-      <c r="F48" s="8">
+      <c r="F48" s="6">
         <v>10</v>
       </c>
       <c r="G48" s="2">
@@ -4091,7 +4088,7 @@
       <c r="B66" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C66" s="8">
+      <c r="C66" s="6">
         <v>39</v>
       </c>
       <c r="D66" s="2">
@@ -4272,13 +4269,13 @@
         <v>8</v>
       </c>
       <c r="M69" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N69" s="2">
         <v>6</v>
       </c>
       <c r="O69" s="2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="P69" s="2">
         <v>5</v>
@@ -4815,7 +4812,7 @@
       <c r="J80" s="2">
         <v>8</v>
       </c>
-      <c r="K80" s="9">
+      <c r="K80" s="2">
         <v>21</v>
       </c>
       <c r="L80" s="2">
@@ -4991,19 +4988,19 @@
       <c r="B84" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C84" s="8">
+      <c r="C84" s="6">
         <v>39</v>
       </c>
       <c r="D84" s="2">
         <v>10</v>
       </c>
-      <c r="E84" s="8">
+      <c r="E84" s="6">
         <v>34</v>
       </c>
       <c r="F84" s="2">
         <v>10</v>
       </c>
-      <c r="G84" s="8">
+      <c r="G84" s="6">
         <v>35</v>
       </c>
       <c r="H84" s="2">
@@ -5697,7 +5694,7 @@
       <c r="D98" s="2">
         <v>8</v>
       </c>
-      <c r="E98" s="8">
+      <c r="E98" s="6">
         <v>25</v>
       </c>
       <c r="F98" s="2">
@@ -6347,7 +6344,7 @@
       <c r="D111" s="2">
         <v>5</v>
       </c>
-      <c r="E111" s="8">
+      <c r="E111" s="6">
         <v>22</v>
       </c>
       <c r="F111" s="2">
@@ -6800,10 +6797,10 @@
       <c r="E120" s="2">
         <v>29</v>
       </c>
-      <c r="F120" s="8">
-        <v>7</v>
-      </c>
-      <c r="G120" s="8">
+      <c r="F120" s="6">
+        <v>7</v>
+      </c>
+      <c r="G120" s="6">
         <v>31</v>
       </c>
       <c r="H120" s="2">
@@ -6947,16 +6944,16 @@
       <c r="D123" s="2">
         <v>9</v>
       </c>
-      <c r="E123" s="8">
+      <c r="E123" s="6">
         <v>30</v>
       </c>
       <c r="F123" s="2">
         <v>8</v>
       </c>
-      <c r="G123" s="8">
+      <c r="G123" s="6">
         <v>29</v>
       </c>
-      <c r="H123" s="8">
+      <c r="H123" s="6">
         <v>10</v>
       </c>
       <c r="I123" s="2">
